--- a/templates/timesheet-template.xlsx
+++ b/templates/timesheet-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Time and Mileage Managment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA1B6792-1F90-FA49-B3D1-D80EC1E856B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C23EF8E-78B2-034A-8EA1-098AA8937248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1825,14 +1825,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1965,10 +1969,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1979,6 +1980,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2000,16 +2007,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2043,6 +2040,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2137,7 +2137,99 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>25200</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>130008</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>108576</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>191808</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B500BB45-2EF0-0859-0C2A-B9C8DFC0316D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="25200" y="4165560"/>
+            <a:ext cx="1326960" cy="671400"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B500BB45-2EF0-0859-0C2A-B9C8DFC0316D}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="16560" y="4156920"/>
+              <a:ext cx="1344600" cy="689040"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-08-30T16:52:30.797"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.05" units="cm"/>
+      <inkml:brushProperty name="height" value="0.05" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">173 725 1456,'0'0'0,"0"0"520,-2 0-184,2 0-96,-2 0-56,1 0-24,1 0-40,-2 0 0,0 0-16,0 0 24,2 0 32,-1 0 48,1 0-208,-2 0 280,0 0 40,1 0 0,-1 0 81,0 0 15,0 0 40,1 0 48,-1 0-16,-2 0 16,1-2-8,1 1-48,-1-1 32,-1 0-56,3 0-31,-3 1 63,1-3-128,1 3 0,-1-3-48,1 2-96,0-1 16,1 0-64,-1-1 40,0 1-64,0-1 16,2-1 0,0 2-48,0-3 16,0 3-16,4-2-24,-1 0 104,1-1-120,-1 1-40,1 0 24,1-2-152,0 2 184,9-2-88,-11 2 40,2-2 40,9 2-72,-9 0 72,9 0-48,-9 0 8,-5 5-8,16-6 8,-11 1 0,10 0-8,-10 0-16,14 0 24,-14 0 24,-5 5-32,21-4 8,-16-1 0,16 2-16,-6-1-8,-1 1-8,0-1 24,-14 4 0,15-3 8,1-1-8,-2 1 40,1-1 16,1 3-56,1-3 8,-17 4-8,15-1 16,3-1 8,-3 0 56,2 0-8,2 1-32,-19 1-40,17-2 48,1 0-8,1 2-32,-2-2 48,2 2-32,0 0 8,-19 0-32,17 0 40,2 0-24,0 0 8,0 0 24,-2 0-8,0 0-40,0 0 0,0 0 0,-1 4 0,-1-4 32,-1 3-16,0 1-48,0-4-8,-9 3 72,14 1 8,-14-1 40,14 1 8,-14-1-72,10 0 8,-9 1-40,7-1 40,-7 1 0,7 1 8,-9 0 24,10 0-16,-11 9 8,11-11-64,-11 3 0,16 18 56,-14-7 8,12 4 32,-13-2-24,10 3-56,-14-1 17,3-1-1,1 1 40,-4-21-56,0 20 32,0 3-32,0-1 8,0-17-80,0 16 40,0-5 32,0-16 0,0 15 8,-2 1 40,0 2-48,-1 1-24,-1 2-8,-1 0 56,5-21-24,-5 22-24,0 2 48,-2 0-129,-7 0 17,9 4 56,-9-2-48,14-26 80,-5 29 72,-12 0-48,10-1-16,-12 1 56,4-2-80,-3 1 72,18-28-56,-17 28 40,-2-3 1,0 1 47,-1 0-48,-3-2 32,-1 2-56,24-26-16,-24 22 40,0 1 0,-4-1-40,1-1 0,-2-1 32,-1-3 24,30-17-56,-29 18 32,-2-1 56,2-3-48,-2-1-16,0-7 16,2 13 16,29-19-56,-31 3 40,2 11-16,-1-14-8,1 5 16,2 0-32,-1-1 32,28-4-32,-26 3 24,2-3 0,2 0-16,-1 0-16,3 0 24,1 0-16,19 0 0,-17-2 16,1 1-8,1-5-32,1 3 64,7-2-96,-10 0-64,17 5 120,-5-6-64,-2 1-8,0 0 72,0-2 128,2 0-128,0-6-48,5 13 48,-6-6-32,1 0-64,4-8 64,-1 9-32,0-11 48,0 11 0,2 5 16,-1-16 0,1 10 48,0-12-72,0 11-8,3-11 24,2 11-40,-5 7 48,5-19-8,9 12-16,-10-12-16,11 5 16,-10 0-16,16 1 8,-21 13 32,15-14-32,1 0 32,1 0 8,0 1-40,2 6 24,0-11-56,-19 18 64,19-6 16,2-10 0,-1 11 112,1-11 56,1 11-56,1-2-48,-23 7-80,22-6 32,-1 0-16,1 1-136,1 2 88,-1-1-40,0 3-16,-22 1 88,23 0 56,1 0-24,0 3-32,0 0 8,0 3 0,0 9 24,-24-15-32,24 5 32,-1 11 0,1-2-16,0-1-48,-2 3 32,0-1-24,-22-15 24,25 17 32,-5 2 0,3-1 8,-3 2 16,1-1-48,-1 2 40,-20-21-48,19 20 40,0 1 24,0 0 24,-2-1-24,2 1 128,14 17-24,-33-38-168,31 33 184,-2-4-16,-3-3-104,-2-4 40,-1-5 8,-3-3-24,-20-14-88,19 5 88,0 9-16,2-14 8,-1 5 64,1-1-40,3-4 8,-24 0-112,22 0 136,3-2-32,0-12 64,3 7-48,-1-13 48,1 1-16,-28 19-152,29-21 176,-1-5 8,1 0-48,-1-3-56,-3-4 32,1-1 8,-26 34-120,28-34 128,-3-4 16,1 0-55,-3-2-105,-1 1 112,0-1 40,-22 40-136,21-38 144,-4 0 88,-1 2-144,1 2 16,-3-1-104,-9 3 56,-5 32-56,17-31 48,-12 0-32,9 0 72,-11 2-40,1 1-56,1 2 32,-5 26-24,3-27 24,1-1-24,-4 2 64,3-1-32,-3-1-16,0 1-8,0 27-8,0-31 16,-3 0-8,-2-2-16,0-1 8,-1-2-48,0-1-16,6 37 64,-14-37-88,9-1-24,-2 0 16,-10 0-16,11 0 96,-11 2-72,17 36 88,-5-36-56,-12 1 8,12 3 32,-13 1 56,12 2 8,-10 1 0,16 28-48,-5-26-48,-9 4 0,7-1-32,-8 6-72,10 0 48,-11 3 8,16 14 96,-5-5-121,-9-10 89,7 11-40,-10-1-88,10 3 56,-12 1-8,19 1 112,-15 0-128,-2 0 40,-4 0-24,-1 13-48,-4-9-56,-2 13 0,28-17 216,-29 15-216,-4 3 8,-1 1-48,-4 1 112,0 4-24,-3 2 56,41-26 112,-19 14-48,-3 1-40,-1 3 8,-1 2 104,0 1 8,-3 1 16,27-22-48,-26 24 88,-2 2-80,2 2 104,-3 3-56,2 0-8,-3 3-16,30-34-32,-29 35-8,2 2 16,-1 0 40,-1 2-40,1 1-32,4-1 88,24-39-64,-24 40 0,3-1 32,3 1 24,-1 0-32,5-3 32,0 1-56,14-38 0,-7 38-8,0-3-56,0-1-128,4 0 88,1-3 8,2 0 8,0-31 88,0 31 16,4-3-48,9-1 48,-7-1-8,14-2 0,-4-1 120,-16-23-128,17 20 88,2-3 0,3-1 16,1-2-24,2-9 56,1 10 48,-26-15-184,52 6 328,1-1-16,1-5 32,-5 0-24,1-14-136,-1-2 8,-49 16-192,44-17 201,1-2 55,-2-1 32,3-4-96,-1-1 24,3-2-104,-48 27-112,49-28 96,-1-3 16,2-1-32,-1-1-120,0-1 128,-49 34-88,50-35 64,-1-1-32,1 2 112,0-1-72,0 1-104,-2 1 64,-48 33-32,49-31 56,-3 0-80,2 0 112,33-22 48,-12 10-112,-18 10-72,-51 33 48,38-20 0,-7 4-104,-1 11 104,-5-11 64,-1 11-40,-3 0-24,-21 5 0,19-5 0,-2 3 32,0 0-48,1 2 16,-1 0 128,0 4-80,-17-4-48,17 3 16,-1 1 8,-3-1-112,-7 2 104,11 9-32,-12-9 32,-5-5-16,17 16 24,-12-2-48,14-1 32,-14 6-8,13 2-40,-13 0 32,-5-21 8,15 24-16,-11-2 32,10 4-16,-14 3-24,5 6-32,-2 2 32,-3-37 24,0 45-24,0 2 8,-3 1 40,-4 3-96,-9 1-32,11 1 64,5-53 40,-17 57-48,3 0 48,-1 0 24,-4 1-88,0-1 64,-4-4-48,23-53 48,-24 52-16,-1 0 8,-3-6-48,-3-1-16,2-4 72,-2-5-40,31-36 40,-33 31-24,2-3 48,-1-9-96,-1-4 8,16-15-32,-6 5-56,23-5 152,-24 4-240,-5-1-88,-2-3-80,-7 0-73,-1-5 17,-8-16 64,47 21 400,-48-20-304,-2-8 112,-2-8 40,1-7 16,-4-5-64,1-9 8,54 57 192,-56-62-256,-1-3-16,-2-2 40,-1-2-96,0 0 80,1 2 40,59 67 208,-56-67-160,-1 5 96,7 5 56,26 29-48,-2 1 40,5 1 0,21 26 16,-22-27 0,3 3 32,-2-2 0,6 3-16,-2 1-48,3 0-56,14 22 88,-14-21-40,9 2-48,-12 0-16,13 2 48,-2 0-48,0 1 23,6 16 81,-5-15 48,0 1 57,3 9 119,2-12 40,0 11 48,0 1 48,0 5-360,5-7 448,20-6 72,-3 11-8,2 0-8,-24 2-504,29 0 480,6 0 16,6 4 25,4 1-1,6 9-72,6-9-48,5 10-72,10-10-64,-72-5-264,76 21 232,8-6-32,4 1-32,5-1 0,15 8-32,85 13-24,-193-36-112,174 33 104,-21-4-64,-41-8 24,-7-1-32,-4 1-88,-10-4 40,-91-17 16,87 21-8,-3-2-24,-7-4 64,-1 2-48,-6-1-32,-4 1 48,-66-17 0,57 15-16,-4 1 0,-7-11 48,-3 14-64,-5-14 32,-2 12-40,-36-17 40,31 6-72,-3 13-72,-6-6-88,-4-8-120,-5 13-176,-9-13-216,-4-5 744,3 5-952,-3 9-185,0-14-159,-3 3-408,-18 1-593,-1-1-639,22-3 2936,-31 0-3209,-11 0-1064,42 0 4273</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2363,114 +2455,114 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="125" t="s">
+      <c r="B1" s="127" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="126"/>
-      <c r="D1" s="126"/>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="117" t="s">
+      <c r="C1" s="128"/>
+      <c r="D1" s="128"/>
+      <c r="E1" s="128"/>
+      <c r="F1" s="128"/>
+      <c r="G1" s="128"/>
+      <c r="H1" s="119" t="s">
         <v>1</v>
       </c>
       <c r="I1" s="63"/>
       <c r="J1" s="63"/>
-      <c r="K1" s="125" t="s">
+      <c r="K1" s="127" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="126"/>
-      <c r="P1" s="126"/>
-      <c r="Q1" s="126"/>
-      <c r="R1" s="126"/>
-      <c r="S1" s="124" t="s">
+      <c r="L1" s="128"/>
+      <c r="M1" s="128"/>
+      <c r="N1" s="128"/>
+      <c r="O1" s="128"/>
+      <c r="P1" s="128"/>
+      <c r="Q1" s="128"/>
+      <c r="R1" s="128"/>
+      <c r="S1" s="126" t="s">
         <v>45</v>
       </c>
       <c r="T1" s="63"/>
       <c r="U1" s="63"/>
       <c r="V1" s="63"/>
-      <c r="W1" s="93">
+      <c r="W1" s="95">
         <f>A18</f>
         <v>46250</v>
       </c>
-      <c r="X1" s="94"/>
-      <c r="Y1" s="94"/>
-      <c r="Z1" s="94"/>
-      <c r="AA1" s="94"/>
+      <c r="X1" s="96"/>
+      <c r="Y1" s="96"/>
+      <c r="Z1" s="96"/>
+      <c r="AA1" s="96"/>
       <c r="AB1" s="34"/>
     </row>
     <row r="2" spans="1:28" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="176" t="s">
+      <c r="B2" s="175" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="72"/>
-      <c r="D2" s="177"/>
+      <c r="D2" s="176"/>
       <c r="E2" s="71"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="131"/>
-      <c r="H2" s="119"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="119"/>
-      <c r="K2" s="120"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="131"/>
-      <c r="P2" s="130"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="105"/>
+      <c r="F2" s="132"/>
+      <c r="G2" s="133"/>
+      <c r="H2" s="121"/>
+      <c r="I2" s="107"/>
+      <c r="J2" s="121"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="132"/>
+      <c r="M2" s="133"/>
+      <c r="N2" s="132"/>
+      <c r="O2" s="133"/>
+      <c r="P2" s="132"/>
+      <c r="Q2" s="133"/>
+      <c r="R2" s="108"/>
+      <c r="S2" s="107"/>
       <c r="T2" s="188"/>
-      <c r="U2" s="108"/>
-      <c r="V2" s="175" t="s">
+      <c r="U2" s="110"/>
+      <c r="V2" s="174" t="s">
         <v>5</v>
       </c>
       <c r="W2" s="63"/>
       <c r="X2" s="64"/>
-      <c r="Y2" s="173" t="s">
+      <c r="Y2" s="172" t="s">
         <v>6</v>
       </c>
       <c r="Z2" s="63"/>
       <c r="AA2" s="63"/>
-      <c r="AB2" s="174"/>
+      <c r="AB2" s="173"/>
     </row>
     <row r="3" spans="1:28" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="187"/>
-      <c r="C3" s="108"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="111"/>
-      <c r="F3" s="89"/>
-      <c r="G3" s="90"/>
-      <c r="H3" s="104"/>
-      <c r="I3" s="105"/>
-      <c r="J3" s="119"/>
-      <c r="K3" s="105"/>
-      <c r="L3" s="104"/>
-      <c r="M3" s="105"/>
-      <c r="N3" s="104"/>
-      <c r="O3" s="105"/>
-      <c r="P3" s="118"/>
-      <c r="Q3" s="105"/>
-      <c r="R3" s="104"/>
-      <c r="S3" s="105"/>
-      <c r="T3" s="107"/>
-      <c r="U3" s="108"/>
+      <c r="C3" s="110"/>
+      <c r="D3" s="112"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="90"/>
+      <c r="G3" s="91"/>
+      <c r="H3" s="106"/>
+      <c r="I3" s="107"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="107"/>
+      <c r="L3" s="106"/>
+      <c r="M3" s="107"/>
+      <c r="N3" s="106"/>
+      <c r="O3" s="107"/>
+      <c r="P3" s="120"/>
+      <c r="Q3" s="107"/>
+      <c r="R3" s="106"/>
+      <c r="S3" s="107"/>
+      <c r="T3" s="109"/>
+      <c r="U3" s="110"/>
       <c r="V3" s="70"/>
       <c r="W3" s="71"/>
       <c r="X3" s="72"/>
       <c r="Y3" s="70"/>
       <c r="Z3" s="71"/>
       <c r="AA3" s="71"/>
-      <c r="AB3" s="120"/>
+      <c r="AB3" s="122"/>
     </row>
     <row r="4" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -2563,61 +2655,79 @@
         <v>17</v>
       </c>
       <c r="B5" s="73"/>
-      <c r="C5" s="101"/>
+      <c r="C5" s="103"/>
       <c r="D5" s="73"/>
-      <c r="E5" s="97"/>
-      <c r="F5" s="171"/>
-      <c r="G5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="170"/>
+      <c r="G5" s="101"/>
       <c r="H5" s="58"/>
-      <c r="I5" s="99"/>
+      <c r="I5" s="101"/>
       <c r="J5" s="58"/>
-      <c r="K5" s="99"/>
+      <c r="K5" s="101"/>
       <c r="L5" s="58"/>
-      <c r="M5" s="97"/>
+      <c r="M5" s="99"/>
       <c r="N5" s="58"/>
-      <c r="O5" s="99"/>
+      <c r="O5" s="101"/>
       <c r="P5" s="58"/>
-      <c r="Q5" s="99"/>
+      <c r="Q5" s="101"/>
       <c r="R5" s="58"/>
-      <c r="S5" s="99"/>
+      <c r="S5" s="101"/>
       <c r="T5" s="58"/>
-      <c r="U5" s="101"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="165"/>
-      <c r="Y5" s="163"/>
-      <c r="Z5" s="78"/>
+      <c r="U5" s="103"/>
+      <c r="V5" s="58">
+        <f>MIN(9, SUM(B5, D5,F5,H5,J5, L5, N5, P5, R5, T5))</f>
+        <v>0</v>
+      </c>
+      <c r="W5" s="105">
+        <f>MAX(0, SUM(B5,D5, F5,H5,J5, L5, N5, P5, R5, T5) - 9)</f>
+        <v>0</v>
+      </c>
+      <c r="X5" s="88">
+        <f>SUM(B5, D5,F5,H5,J5, L5, N5, P5, R5, T5)</f>
+        <v>0</v>
+      </c>
+      <c r="Y5" s="152">
+        <f>C5</f>
+        <v>0</v>
+      </c>
+      <c r="Z5" s="78">
+        <f>SUM(E5+G5+I5+K5+M5+O5+Q5+S5+U5)</f>
+        <v>0</v>
+      </c>
       <c r="AA5" s="78"/>
-      <c r="AB5" s="52"/>
+      <c r="AB5" s="52">
+        <f>SUM(Y5+Z5+AA5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="6" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="38">
         <v>46244</v>
       </c>
       <c r="B6" s="74"/>
-      <c r="C6" s="102"/>
+      <c r="C6" s="104"/>
       <c r="D6" s="74"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="172"/>
-      <c r="G6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="171"/>
+      <c r="G6" s="102"/>
       <c r="H6" s="59"/>
-      <c r="I6" s="100"/>
+      <c r="I6" s="102"/>
       <c r="J6" s="59"/>
-      <c r="K6" s="100"/>
+      <c r="K6" s="102"/>
       <c r="L6" s="59"/>
-      <c r="M6" s="98"/>
+      <c r="M6" s="100"/>
       <c r="N6" s="59"/>
-      <c r="O6" s="100"/>
+      <c r="O6" s="102"/>
       <c r="P6" s="59"/>
-      <c r="Q6" s="100"/>
+      <c r="Q6" s="102"/>
       <c r="R6" s="59"/>
-      <c r="S6" s="100"/>
+      <c r="S6" s="102"/>
       <c r="T6" s="59"/>
-      <c r="U6" s="102"/>
+      <c r="U6" s="104"/>
       <c r="V6" s="59"/>
       <c r="W6" s="79"/>
-      <c r="X6" s="164"/>
-      <c r="Y6" s="164"/>
+      <c r="X6" s="89"/>
+      <c r="Y6" s="89"/>
       <c r="Z6" s="79"/>
       <c r="AA6" s="79"/>
       <c r="AB6" s="53"/>
@@ -2627,32 +2737,50 @@
         <v>18</v>
       </c>
       <c r="B7" s="73"/>
-      <c r="C7" s="101"/>
+      <c r="C7" s="103"/>
       <c r="D7" s="73"/>
-      <c r="E7" s="97"/>
-      <c r="F7" s="171"/>
-      <c r="G7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="170"/>
+      <c r="G7" s="101"/>
       <c r="H7" s="58"/>
-      <c r="I7" s="99"/>
+      <c r="I7" s="101"/>
       <c r="J7" s="58"/>
-      <c r="K7" s="99"/>
+      <c r="K7" s="101"/>
       <c r="L7" s="58"/>
-      <c r="M7" s="97"/>
+      <c r="M7" s="99"/>
       <c r="N7" s="58"/>
-      <c r="O7" s="99"/>
+      <c r="O7" s="101"/>
       <c r="P7" s="58"/>
-      <c r="Q7" s="99"/>
+      <c r="Q7" s="101"/>
       <c r="R7" s="58"/>
-      <c r="S7" s="99"/>
+      <c r="S7" s="101"/>
       <c r="T7" s="58"/>
-      <c r="U7" s="101"/>
-      <c r="V7" s="165"/>
-      <c r="W7" s="103"/>
-      <c r="X7" s="97"/>
-      <c r="Y7" s="163"/>
-      <c r="Z7" s="78"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="58">
+        <f>MIN(9, SUM(B7, D7,F7,H7,J7, L7, N7, P7, R7, T7))</f>
+        <v>0</v>
+      </c>
+      <c r="W7" s="105">
+        <f>MAX(0, SUM(B7,D7, F7,H7,J7, L7, N7, P7, R7, T7) - 9)</f>
+        <v>0</v>
+      </c>
+      <c r="X7" s="88">
+        <f>SUM(B7, D7,F7,H7,J7, L7, N7, P7, R7, T7)</f>
+        <v>0</v>
+      </c>
+      <c r="Y7" s="152">
+        <f t="shared" ref="Y7:Y14" si="0">C7</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="78">
+        <f t="shared" ref="Z7:Z14" si="1">SUM(E7+G7+I7+K7+M7+O7+Q7+S7+U7)</f>
+        <v>0</v>
+      </c>
       <c r="AA7" s="78"/>
-      <c r="AB7" s="52"/>
+      <c r="AB7" s="52">
+        <f t="shared" ref="AB7" si="2">SUM(Y7+Z7+AA7)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="8" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="38">
@@ -2660,29 +2788,29 @@
         <v>46245</v>
       </c>
       <c r="B8" s="74"/>
-      <c r="C8" s="102"/>
+      <c r="C8" s="104"/>
       <c r="D8" s="74"/>
-      <c r="E8" s="98"/>
-      <c r="F8" s="172"/>
-      <c r="G8" s="100"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="171"/>
+      <c r="G8" s="102"/>
       <c r="H8" s="59"/>
-      <c r="I8" s="100"/>
+      <c r="I8" s="102"/>
       <c r="J8" s="59"/>
-      <c r="K8" s="100"/>
+      <c r="K8" s="102"/>
       <c r="L8" s="59"/>
-      <c r="M8" s="98"/>
+      <c r="M8" s="100"/>
       <c r="N8" s="59"/>
-      <c r="O8" s="100"/>
+      <c r="O8" s="102"/>
       <c r="P8" s="59"/>
-      <c r="Q8" s="100"/>
+      <c r="Q8" s="102"/>
       <c r="R8" s="59"/>
-      <c r="S8" s="100"/>
+      <c r="S8" s="102"/>
       <c r="T8" s="59"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="164"/>
+      <c r="U8" s="104"/>
+      <c r="V8" s="59"/>
       <c r="W8" s="79"/>
-      <c r="X8" s="98"/>
-      <c r="Y8" s="164"/>
+      <c r="X8" s="89"/>
+      <c r="Y8" s="89"/>
       <c r="Z8" s="79"/>
       <c r="AA8" s="79"/>
       <c r="AB8" s="53"/>
@@ -2692,32 +2820,50 @@
         <v>19</v>
       </c>
       <c r="B9" s="73"/>
-      <c r="C9" s="101"/>
+      <c r="C9" s="103"/>
       <c r="D9" s="73"/>
-      <c r="E9" s="97"/>
-      <c r="F9" s="171"/>
-      <c r="G9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="170"/>
+      <c r="G9" s="101"/>
       <c r="H9" s="58"/>
-      <c r="I9" s="99"/>
+      <c r="I9" s="101"/>
       <c r="J9" s="58"/>
-      <c r="K9" s="99"/>
+      <c r="K9" s="101"/>
       <c r="L9" s="58"/>
-      <c r="M9" s="97"/>
+      <c r="M9" s="99"/>
       <c r="N9" s="58"/>
-      <c r="O9" s="99"/>
+      <c r="O9" s="101"/>
       <c r="P9" s="58"/>
-      <c r="Q9" s="99"/>
+      <c r="Q9" s="101"/>
       <c r="R9" s="58"/>
-      <c r="S9" s="99"/>
+      <c r="S9" s="101"/>
       <c r="T9" s="58"/>
-      <c r="U9" s="101"/>
-      <c r="V9" s="165"/>
-      <c r="W9" s="103"/>
-      <c r="X9" s="97"/>
-      <c r="Y9" s="163"/>
-      <c r="Z9" s="78"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="58">
+        <f>MIN(9, SUM(B9, D9,F9,H9,J9, L9, N9, P9, R9, T9))</f>
+        <v>0</v>
+      </c>
+      <c r="W9" s="105">
+        <f>MAX(0, SUM(B9,D9, F9,H9,J9, L9, N9, P9, R9, T9) - 9)</f>
+        <v>0</v>
+      </c>
+      <c r="X9" s="88">
+        <f>SUM(B9, D9,F9,H9,J9, L9, N9, P9, R9, T9)</f>
+        <v>0</v>
+      </c>
+      <c r="Y9" s="152">
+        <f t="shared" ref="Y9:Y14" si="3">C9</f>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="78">
+        <f t="shared" ref="Z9:Z14" si="4">SUM(E9+G9+I9+K9+M9+O9+Q9+S9+U9)</f>
+        <v>0</v>
+      </c>
       <c r="AA9" s="78"/>
-      <c r="AB9" s="52"/>
+      <c r="AB9" s="52">
+        <f t="shared" ref="AB9" si="5">SUM(Y9+Z9+AA9)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="38">
@@ -2725,29 +2871,29 @@
         <v>46246</v>
       </c>
       <c r="B10" s="74"/>
-      <c r="C10" s="102"/>
+      <c r="C10" s="104"/>
       <c r="D10" s="74"/>
-      <c r="E10" s="98"/>
-      <c r="F10" s="172"/>
-      <c r="G10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="102"/>
       <c r="H10" s="59"/>
-      <c r="I10" s="100"/>
+      <c r="I10" s="102"/>
       <c r="J10" s="59"/>
-      <c r="K10" s="100"/>
+      <c r="K10" s="102"/>
       <c r="L10" s="59"/>
-      <c r="M10" s="98"/>
+      <c r="M10" s="100"/>
       <c r="N10" s="59"/>
-      <c r="O10" s="100"/>
+      <c r="O10" s="102"/>
       <c r="P10" s="59"/>
-      <c r="Q10" s="100"/>
+      <c r="Q10" s="102"/>
       <c r="R10" s="59"/>
-      <c r="S10" s="100"/>
+      <c r="S10" s="102"/>
       <c r="T10" s="59"/>
-      <c r="U10" s="102"/>
-      <c r="V10" s="164"/>
+      <c r="U10" s="104"/>
+      <c r="V10" s="59"/>
       <c r="W10" s="79"/>
-      <c r="X10" s="98"/>
-      <c r="Y10" s="164"/>
+      <c r="X10" s="89"/>
+      <c r="Y10" s="89"/>
       <c r="Z10" s="79"/>
       <c r="AA10" s="79"/>
       <c r="AB10" s="53"/>
@@ -2756,18 +2902,18 @@
       <c r="A11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="169"/>
-      <c r="C11" s="95"/>
+      <c r="B11" s="168"/>
+      <c r="C11" s="97"/>
       <c r="D11" s="73"/>
-      <c r="E11" s="97"/>
-      <c r="F11" s="171"/>
-      <c r="G11" s="99"/>
+      <c r="E11" s="99"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="101"/>
       <c r="H11" s="58"/>
-      <c r="I11" s="99"/>
+      <c r="I11" s="101"/>
       <c r="J11" s="58"/>
-      <c r="K11" s="99"/>
+      <c r="K11" s="101"/>
       <c r="L11" s="58"/>
-      <c r="M11" s="97"/>
+      <c r="M11" s="99"/>
       <c r="N11" s="54"/>
       <c r="O11" s="60"/>
       <c r="P11" s="54"/>
@@ -2776,31 +2922,49 @@
       <c r="S11" s="60"/>
       <c r="T11" s="54"/>
       <c r="U11" s="75"/>
-      <c r="V11" s="84"/>
-      <c r="W11" s="156"/>
-      <c r="X11" s="86"/>
-      <c r="Y11" s="150"/>
-      <c r="Z11" s="82"/>
+      <c r="V11" s="58">
+        <f>MIN(9, SUM(B11, D11,F11,H11,J11, L11, N11, P11, R11, T11))</f>
+        <v>0</v>
+      </c>
+      <c r="W11" s="105">
+        <f>MAX(0, SUM(B11,D11, F11,H11,J11, L11, N11, P11, R11, T11) - 9)</f>
+        <v>0</v>
+      </c>
+      <c r="X11" s="88">
+        <f>SUM(B11, D11,F11,H11,J11, L11, N11, P11, R11, T11)</f>
+        <v>0</v>
+      </c>
+      <c r="Y11" s="152">
+        <f t="shared" ref="Y11:Y14" si="6">C11</f>
+        <v>0</v>
+      </c>
+      <c r="Z11" s="78">
+        <f t="shared" ref="Z11:Z14" si="7">SUM(E11+G11+I11+K11+M11+O11+Q11+S11+U11)</f>
+        <v>0</v>
+      </c>
       <c r="AA11" s="82"/>
-      <c r="AB11" s="86"/>
+      <c r="AB11" s="52">
+        <f t="shared" ref="AB11" si="8">SUM(Y11+Z11+AA11)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="38">
         <f>A10+1</f>
         <v>46247</v>
       </c>
-      <c r="B12" s="170"/>
-      <c r="C12" s="96"/>
+      <c r="B12" s="169"/>
+      <c r="C12" s="98"/>
       <c r="D12" s="74"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="172"/>
-      <c r="G12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="171"/>
+      <c r="G12" s="102"/>
       <c r="H12" s="59"/>
-      <c r="I12" s="100"/>
+      <c r="I12" s="102"/>
       <c r="J12" s="59"/>
-      <c r="K12" s="100"/>
+      <c r="K12" s="102"/>
       <c r="L12" s="59"/>
-      <c r="M12" s="98"/>
+      <c r="M12" s="100"/>
       <c r="N12" s="55"/>
       <c r="O12" s="81"/>
       <c r="P12" s="55"/>
@@ -2809,30 +2973,30 @@
       <c r="S12" s="81"/>
       <c r="T12" s="55"/>
       <c r="U12" s="76"/>
-      <c r="V12" s="91"/>
-      <c r="W12" s="166"/>
-      <c r="X12" s="88"/>
-      <c r="Y12" s="151"/>
-      <c r="Z12" s="83"/>
+      <c r="V12" s="59"/>
+      <c r="W12" s="79"/>
+      <c r="X12" s="89"/>
+      <c r="Y12" s="89"/>
+      <c r="Z12" s="79"/>
       <c r="AA12" s="83"/>
-      <c r="AB12" s="88"/>
+      <c r="AB12" s="53"/>
     </row>
     <row r="13" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="167"/>
+      <c r="B13" s="166"/>
       <c r="C13" s="75"/>
       <c r="D13" s="73"/>
-      <c r="E13" s="97"/>
-      <c r="F13" s="171"/>
-      <c r="G13" s="99"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="170"/>
+      <c r="G13" s="101"/>
       <c r="H13" s="58"/>
-      <c r="I13" s="99"/>
+      <c r="I13" s="101"/>
       <c r="J13" s="58"/>
-      <c r="K13" s="99"/>
+      <c r="K13" s="101"/>
       <c r="L13" s="58"/>
-      <c r="M13" s="97"/>
+      <c r="M13" s="99"/>
       <c r="N13" s="54"/>
       <c r="O13" s="60"/>
       <c r="P13" s="54"/>
@@ -2841,13 +3005,31 @@
       <c r="S13" s="60"/>
       <c r="T13" s="54"/>
       <c r="U13" s="75"/>
-      <c r="V13" s="84"/>
-      <c r="W13" s="156"/>
-      <c r="X13" s="86"/>
-      <c r="Y13" s="150"/>
-      <c r="Z13" s="82"/>
+      <c r="V13" s="58">
+        <f>MIN(9, SUM(B13, D13,F13,H13,J13, L13, N13, P13, R13, T13))</f>
+        <v>0</v>
+      </c>
+      <c r="W13" s="105">
+        <f>MAX(0, SUM(B13,D13, F13,H13,J13, L13, N13, P13, R13, T13) - 9)</f>
+        <v>0</v>
+      </c>
+      <c r="X13" s="88">
+        <f>SUM(B13, D13,F13,H13,J13, L13, N13, P13, R13, T13)</f>
+        <v>0</v>
+      </c>
+      <c r="Y13" s="152">
+        <f t="shared" ref="Y13:Y14" si="9">C13</f>
+        <v>0</v>
+      </c>
+      <c r="Z13" s="78">
+        <f t="shared" ref="Z13:Z14" si="10">SUM(E13+G13+I13+K13+M13+O13+Q13+S13+U13)</f>
+        <v>0</v>
+      </c>
       <c r="AA13" s="82"/>
-      <c r="AB13" s="86"/>
+      <c r="AB13" s="52">
+        <f t="shared" ref="AB13" si="11">SUM(Y13+Z13+AA13)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="38">
@@ -2857,15 +3039,15 @@
       <c r="B14" s="182"/>
       <c r="C14" s="76"/>
       <c r="D14" s="74"/>
-      <c r="E14" s="98"/>
-      <c r="F14" s="172"/>
-      <c r="G14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="171"/>
+      <c r="G14" s="102"/>
       <c r="H14" s="59"/>
-      <c r="I14" s="100"/>
+      <c r="I14" s="102"/>
       <c r="J14" s="59"/>
-      <c r="K14" s="100"/>
+      <c r="K14" s="102"/>
       <c r="L14" s="59"/>
-      <c r="M14" s="98"/>
+      <c r="M14" s="100"/>
       <c r="N14" s="55"/>
       <c r="O14" s="81"/>
       <c r="P14" s="55"/>
@@ -2874,21 +3056,21 @@
       <c r="S14" s="81"/>
       <c r="T14" s="55"/>
       <c r="U14" s="76"/>
-      <c r="V14" s="91"/>
-      <c r="W14" s="166"/>
-      <c r="X14" s="88"/>
-      <c r="Y14" s="151"/>
-      <c r="Z14" s="83"/>
+      <c r="V14" s="59"/>
+      <c r="W14" s="79"/>
+      <c r="X14" s="89"/>
+      <c r="Y14" s="89"/>
+      <c r="Z14" s="79"/>
       <c r="AA14" s="83"/>
-      <c r="AB14" s="88"/>
+      <c r="AB14" s="53"/>
     </row>
     <row r="15" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="167"/>
+      <c r="B15" s="166"/>
       <c r="C15" s="75"/>
-      <c r="D15" s="167"/>
+      <c r="D15" s="166"/>
       <c r="E15" s="60"/>
       <c r="F15" s="54"/>
       <c r="G15" s="60"/>
@@ -2907,9 +3089,9 @@
       <c r="T15" s="54"/>
       <c r="U15" s="75"/>
       <c r="V15" s="84"/>
-      <c r="W15" s="156"/>
+      <c r="W15" s="159"/>
       <c r="X15" s="86"/>
-      <c r="Y15" s="150"/>
+      <c r="Y15" s="157"/>
       <c r="Z15" s="82"/>
       <c r="AA15" s="82"/>
       <c r="AB15" s="86"/>
@@ -2926,7 +3108,7 @@
       <c r="F16" s="55"/>
       <c r="G16" s="81"/>
       <c r="H16" s="55"/>
-      <c r="I16" s="179"/>
+      <c r="I16" s="178"/>
       <c r="J16" s="55"/>
       <c r="K16" s="81"/>
       <c r="L16" s="55"/>
@@ -2939,23 +3121,23 @@
       <c r="S16" s="81"/>
       <c r="T16" s="55"/>
       <c r="U16" s="76"/>
-      <c r="V16" s="91"/>
-      <c r="W16" s="166"/>
-      <c r="X16" s="88"/>
-      <c r="Y16" s="151"/>
+      <c r="V16" s="92"/>
+      <c r="W16" s="179"/>
+      <c r="X16" s="93"/>
+      <c r="Y16" s="158"/>
       <c r="Z16" s="83"/>
       <c r="AA16" s="83"/>
-      <c r="AB16" s="88"/>
+      <c r="AB16" s="93"/>
     </row>
     <row r="17" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="167"/>
+      <c r="B17" s="166"/>
       <c r="C17" s="75"/>
-      <c r="D17" s="167"/>
+      <c r="D17" s="166"/>
       <c r="E17" s="56"/>
-      <c r="F17" s="127"/>
+      <c r="F17" s="129"/>
       <c r="G17" s="60"/>
       <c r="H17" s="54"/>
       <c r="I17" s="183"/>
@@ -2972,9 +3154,9 @@
       <c r="T17" s="54"/>
       <c r="U17" s="75"/>
       <c r="V17" s="84"/>
-      <c r="W17" s="156"/>
+      <c r="W17" s="159"/>
       <c r="X17" s="86"/>
-      <c r="Y17" s="150"/>
+      <c r="Y17" s="157"/>
       <c r="Z17" s="82"/>
       <c r="AA17" s="82"/>
       <c r="AB17" s="86"/>
@@ -2984,32 +3166,32 @@
         <f>A16+1</f>
         <v>46250</v>
       </c>
-      <c r="B18" s="168"/>
-      <c r="C18" s="129"/>
-      <c r="D18" s="168"/>
+      <c r="B18" s="167"/>
+      <c r="C18" s="131"/>
+      <c r="D18" s="167"/>
       <c r="E18" s="57"/>
-      <c r="F18" s="128"/>
+      <c r="F18" s="130"/>
       <c r="G18" s="61"/>
-      <c r="H18" s="159"/>
-      <c r="I18" s="109"/>
+      <c r="H18" s="162"/>
+      <c r="I18" s="111"/>
       <c r="J18" s="80"/>
-      <c r="K18" s="109"/>
+      <c r="K18" s="111"/>
       <c r="L18" s="80"/>
-      <c r="M18" s="109"/>
-      <c r="N18" s="159"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="162"/>
       <c r="O18" s="61"/>
-      <c r="P18" s="159"/>
-      <c r="Q18" s="109"/>
+      <c r="P18" s="162"/>
+      <c r="Q18" s="111"/>
       <c r="R18" s="80"/>
-      <c r="S18" s="109"/>
+      <c r="S18" s="111"/>
       <c r="T18" s="80"/>
-      <c r="U18" s="129"/>
+      <c r="U18" s="131"/>
       <c r="V18" s="85"/>
-      <c r="W18" s="157"/>
+      <c r="W18" s="160"/>
       <c r="X18" s="87"/>
-      <c r="Y18" s="162"/>
-      <c r="Z18" s="92"/>
-      <c r="AA18" s="92"/>
+      <c r="Y18" s="165"/>
+      <c r="Z18" s="94"/>
+      <c r="AA18" s="94"/>
       <c r="AB18" s="87"/>
     </row>
     <row r="19" spans="1:28" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
@@ -3017,107 +3199,107 @@
         <v>24</v>
       </c>
       <c r="B19" s="13">
-        <f t="shared" ref="B19:AA19" si="0">SUM(B5:B18)</f>
+        <f t="shared" ref="B19:AA19" si="12">SUM(B5:B18)</f>
         <v>0</v>
       </c>
       <c r="C19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="E19" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="F19" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="G19" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="H19" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="I19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="J19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="K19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="L19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="M19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="N19" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="O19" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="P19" s="30">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Q19" s="33">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="R19" s="32">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="S19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="T19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U19" s="13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="V19" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="W19" s="15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="X19" s="14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Y19" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="Z19" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AA19" s="16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="AB19" s="16">
@@ -3181,51 +3363,51 @@
       <c r="S21" s="19"/>
       <c r="T21" s="19"/>
       <c r="U21" s="20"/>
-      <c r="V21" s="153" t="s">
+      <c r="V21" s="154" t="s">
         <v>27</v>
       </c>
-      <c r="W21" s="154"/>
-      <c r="X21" s="155"/>
-      <c r="Y21" s="143" t="s">
+      <c r="W21" s="155"/>
+      <c r="X21" s="156"/>
+      <c r="Y21" s="145" t="s">
         <v>28</v>
       </c>
-      <c r="Z21" s="144"/>
-      <c r="AA21" s="160"/>
-      <c r="AB21" s="155"/>
+      <c r="Z21" s="146"/>
+      <c r="AA21" s="163"/>
+      <c r="AB21" s="156"/>
     </row>
     <row r="22" spans="1:28" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="152"/>
-      <c r="C22" s="113"/>
-      <c r="D22" s="152"/>
-      <c r="E22" s="113"/>
-      <c r="F22" s="152"/>
-      <c r="G22" s="113"/>
-      <c r="H22" s="152"/>
-      <c r="I22" s="113"/>
-      <c r="J22" s="112"/>
-      <c r="K22" s="113"/>
-      <c r="L22" s="112"/>
-      <c r="M22" s="113"/>
-      <c r="N22" s="112"/>
-      <c r="O22" s="113"/>
-      <c r="P22" s="112"/>
-      <c r="Q22" s="113"/>
-      <c r="R22" s="112"/>
-      <c r="S22" s="113"/>
-      <c r="T22" s="158"/>
+      <c r="B22" s="153"/>
+      <c r="C22" s="115"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="115"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="115"/>
+      <c r="H22" s="153"/>
+      <c r="I22" s="115"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="115"/>
+      <c r="L22" s="114"/>
+      <c r="M22" s="115"/>
+      <c r="N22" s="114"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="114"/>
+      <c r="Q22" s="115"/>
+      <c r="R22" s="114"/>
+      <c r="S22" s="115"/>
+      <c r="T22" s="161"/>
       <c r="U22" s="72"/>
-      <c r="V22" s="145"/>
+      <c r="V22" s="147"/>
       <c r="W22" s="71"/>
       <c r="X22" s="71"/>
-      <c r="Y22" s="134" t="s">
+      <c r="Y22" s="136" t="s">
         <v>30</v>
       </c>
-      <c r="Z22" s="135"/>
-      <c r="AA22" s="142"/>
-      <c r="AB22" s="102"/>
+      <c r="Z22" s="137"/>
+      <c r="AA22" s="144"/>
+      <c r="AB22" s="104"/>
     </row>
     <row r="23" spans="1:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="46"/>
@@ -3237,7 +3419,7 @@
       </c>
       <c r="E23" s="40"/>
       <c r="F23" s="41"/>
-      <c r="G23" s="133"/>
+      <c r="G23" s="135"/>
       <c r="H23" s="63"/>
       <c r="I23" s="63"/>
       <c r="J23" s="63"/>
@@ -3257,15 +3439,15 @@
       <c r="V23" s="63"/>
       <c r="W23" s="63"/>
       <c r="X23" s="63"/>
-      <c r="Y23" s="134" t="s">
+      <c r="Y23" s="136" t="s">
         <v>32</v>
       </c>
-      <c r="Z23" s="116"/>
-      <c r="AA23" s="140">
+      <c r="Z23" s="118"/>
+      <c r="AA23" s="142">
         <f>AB19</f>
         <v>0</v>
       </c>
-      <c r="AB23" s="122"/>
+      <c r="AB23" s="124"/>
     </row>
     <row r="24" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="48"/>
@@ -3282,7 +3464,7 @@
       <c r="L24" s="68"/>
       <c r="M24" s="68"/>
       <c r="N24" s="69"/>
-      <c r="O24" s="149" t="s">
+      <c r="O24" s="151" t="s">
         <v>33</v>
       </c>
       <c r="P24" s="68"/>
@@ -3298,10 +3480,10 @@
         <v>35</v>
       </c>
       <c r="X24" s="27"/>
-      <c r="Y24" s="146"/>
-      <c r="Z24" s="147"/>
-      <c r="AA24" s="141"/>
-      <c r="AB24" s="102"/>
+      <c r="Y24" s="148"/>
+      <c r="Z24" s="149"/>
+      <c r="AA24" s="143"/>
+      <c r="AB24" s="104"/>
     </row>
     <row r="25" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="50"/>
@@ -3323,84 +3505,84 @@
       </c>
       <c r="P25" s="68"/>
       <c r="Q25" s="186"/>
-      <c r="R25" s="98"/>
-      <c r="S25" s="98"/>
-      <c r="T25" s="98"/>
-      <c r="U25" s="98"/>
-      <c r="V25" s="98"/>
-      <c r="W25" s="98"/>
-      <c r="X25" s="102"/>
-      <c r="Y25" s="134" t="s">
+      <c r="R25" s="100"/>
+      <c r="S25" s="100"/>
+      <c r="T25" s="100"/>
+      <c r="U25" s="100"/>
+      <c r="V25" s="100"/>
+      <c r="W25" s="100"/>
+      <c r="X25" s="104"/>
+      <c r="Y25" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="Z25" s="135"/>
-      <c r="AA25" s="140">
+      <c r="Z25" s="137"/>
+      <c r="AA25" s="142">
         <f>Y19+Z19</f>
         <v>0</v>
       </c>
-      <c r="AB25" s="138"/>
+      <c r="AB25" s="140"/>
     </row>
     <row r="26" spans="1:28" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="114" t="s">
+      <c r="A26" s="116" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="115"/>
-      <c r="C26" s="116"/>
-      <c r="D26" s="121" t="s">
+      <c r="B26" s="117"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="115"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="114" t="s">
+      <c r="E26" s="117"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="116" t="s">
         <v>39</v>
       </c>
-      <c r="H26" s="115"/>
-      <c r="I26" s="115"/>
-      <c r="J26" s="115"/>
-      <c r="K26" s="116"/>
-      <c r="L26" s="121" t="s">
+      <c r="H26" s="117"/>
+      <c r="I26" s="117"/>
+      <c r="J26" s="117"/>
+      <c r="K26" s="118"/>
+      <c r="L26" s="123" t="s">
         <v>35</v>
       </c>
-      <c r="M26" s="115"/>
-      <c r="N26" s="122"/>
+      <c r="M26" s="117"/>
+      <c r="N26" s="124"/>
       <c r="O26" s="184" t="s">
         <v>40</v>
       </c>
       <c r="P26" s="68"/>
-      <c r="Q26" s="136"/>
-      <c r="R26" s="137"/>
-      <c r="S26" s="137"/>
-      <c r="T26" s="137"/>
-      <c r="U26" s="137"/>
-      <c r="V26" s="137"/>
-      <c r="W26" s="137"/>
-      <c r="X26" s="138"/>
-      <c r="Y26" s="161" t="s">
+      <c r="Q26" s="138"/>
+      <c r="R26" s="139"/>
+      <c r="S26" s="139"/>
+      <c r="T26" s="139"/>
+      <c r="U26" s="139"/>
+      <c r="V26" s="139"/>
+      <c r="W26" s="139"/>
+      <c r="X26" s="140"/>
+      <c r="Y26" s="164" t="s">
         <v>41</v>
       </c>
-      <c r="Z26" s="116"/>
-      <c r="AA26" s="139">
+      <c r="Z26" s="118"/>
+      <c r="AA26" s="141">
         <f>AA23-AA25</f>
         <v>0</v>
       </c>
-      <c r="AB26" s="122"/>
+      <c r="AB26" s="124"/>
     </row>
     <row r="27" spans="1:28" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="70"/>
       <c r="B27" s="71"/>
-      <c r="C27" s="113"/>
-      <c r="D27" s="123"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="125"/>
       <c r="E27" s="71"/>
       <c r="F27" s="72"/>
       <c r="G27" s="70"/>
       <c r="H27" s="71"/>
       <c r="I27" s="71"/>
       <c r="J27" s="71"/>
-      <c r="K27" s="113"/>
-      <c r="L27" s="123"/>
+      <c r="K27" s="115"/>
+      <c r="L27" s="125"/>
       <c r="M27" s="71"/>
       <c r="N27" s="72"/>
-      <c r="O27" s="148"/>
+      <c r="O27" s="150"/>
       <c r="P27" s="71"/>
       <c r="Q27" s="71"/>
       <c r="R27" s="71"/>
@@ -3411,12 +3593,12 @@
       <c r="W27" s="71"/>
       <c r="X27" s="72"/>
       <c r="Y27" s="70"/>
-      <c r="Z27" s="113"/>
-      <c r="AA27" s="123"/>
+      <c r="Z27" s="115"/>
+      <c r="AA27" s="125"/>
       <c r="AB27" s="72"/>
     </row>
     <row r="28" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="178"/>
+      <c r="A28" s="177"/>
       <c r="B28" s="63"/>
       <c r="C28" s="63"/>
       <c r="D28" s="63"/>
@@ -3441,7 +3623,7 @@
       <c r="U28" s="63"/>
       <c r="V28" s="63"/>
       <c r="W28" s="64"/>
-      <c r="X28" s="132" t="s">
+      <c r="X28" s="134" t="s">
         <v>43</v>
       </c>
       <c r="Y28" s="68"/>

--- a/templates/timesheet-template.xlsx
+++ b/templates/timesheet-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Time and Mileage Managment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C23EF8E-78B2-034A-8EA1-098AA8937248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E3C6855-6F1E-0841-AC8E-5D95C1C3A91C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1702,234 +1702,241 @@
     <xf numFmtId="166" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="75" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="55" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="58" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1969,108 +1976,101 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="94" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="17" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="77" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="11" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2455,114 +2455,114 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="127" t="s">
+      <c r="B1" s="100" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="128"/>
-      <c r="D1" s="128"/>
-      <c r="E1" s="128"/>
-      <c r="F1" s="128"/>
-      <c r="G1" s="128"/>
-      <c r="H1" s="119" t="s">
+      <c r="C1" s="101"/>
+      <c r="D1" s="101"/>
+      <c r="E1" s="101"/>
+      <c r="F1" s="101"/>
+      <c r="G1" s="101"/>
+      <c r="H1" s="157" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="127" t="s">
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="128"/>
-      <c r="M1" s="128"/>
-      <c r="N1" s="128"/>
-      <c r="O1" s="128"/>
-      <c r="P1" s="128"/>
-      <c r="Q1" s="128"/>
-      <c r="R1" s="128"/>
-      <c r="S1" s="126" t="s">
+      <c r="L1" s="101"/>
+      <c r="M1" s="101"/>
+      <c r="N1" s="101"/>
+      <c r="O1" s="101"/>
+      <c r="P1" s="101"/>
+      <c r="Q1" s="101"/>
+      <c r="R1" s="101"/>
+      <c r="S1" s="159" t="s">
         <v>45</v>
       </c>
-      <c r="T1" s="63"/>
-      <c r="U1" s="63"/>
-      <c r="V1" s="63"/>
-      <c r="W1" s="95">
+      <c r="T1" s="86"/>
+      <c r="U1" s="86"/>
+      <c r="V1" s="86"/>
+      <c r="W1" s="166">
         <f>A18</f>
         <v>46250</v>
       </c>
-      <c r="X1" s="96"/>
-      <c r="Y1" s="96"/>
-      <c r="Z1" s="96"/>
-      <c r="AA1" s="96"/>
+      <c r="X1" s="167"/>
+      <c r="Y1" s="167"/>
+      <c r="Z1" s="167"/>
+      <c r="AA1" s="167"/>
       <c r="AB1" s="34"/>
     </row>
     <row r="2" spans="1:28" ht="26.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="175" t="s">
+      <c r="B2" s="112" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="176"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="132"/>
-      <c r="G2" s="133"/>
-      <c r="H2" s="121"/>
-      <c r="I2" s="107"/>
-      <c r="J2" s="121"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="132"/>
-      <c r="M2" s="133"/>
-      <c r="N2" s="132"/>
-      <c r="O2" s="133"/>
-      <c r="P2" s="132"/>
-      <c r="Q2" s="133"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="107"/>
-      <c r="T2" s="188"/>
-      <c r="U2" s="110"/>
-      <c r="V2" s="174" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="170"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="56"/>
+      <c r="U2" s="55"/>
+      <c r="V2" s="111" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="63"/>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="172" t="s">
+      <c r="W2" s="86"/>
+      <c r="X2" s="87"/>
+      <c r="Y2" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="Z2" s="63"/>
-      <c r="AA2" s="63"/>
-      <c r="AB2" s="173"/>
+      <c r="Z2" s="86"/>
+      <c r="AA2" s="86"/>
+      <c r="AB2" s="109"/>
     </row>
     <row r="3" spans="1:28" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="187"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="90"/>
-      <c r="G3" s="91"/>
-      <c r="H3" s="106"/>
-      <c r="I3" s="107"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="107"/>
-      <c r="L3" s="106"/>
-      <c r="M3" s="107"/>
-      <c r="N3" s="106"/>
-      <c r="O3" s="107"/>
-      <c r="P3" s="120"/>
-      <c r="Q3" s="107"/>
-      <c r="R3" s="106"/>
-      <c r="S3" s="107"/>
-      <c r="T3" s="109"/>
-      <c r="U3" s="110"/>
-      <c r="V3" s="70"/>
-      <c r="W3" s="71"/>
-      <c r="X3" s="72"/>
-      <c r="Y3" s="70"/>
-      <c r="Z3" s="71"/>
-      <c r="AA3" s="71"/>
-      <c r="AB3" s="122"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="155"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="162"/>
+      <c r="G3" s="163"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="129"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="158"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="171"/>
+      <c r="U3" s="55"/>
+      <c r="V3" s="89"/>
+      <c r="W3" s="77"/>
+      <c r="X3" s="78"/>
+      <c r="Y3" s="89"/>
+      <c r="Z3" s="77"/>
+      <c r="AA3" s="77"/>
+      <c r="AB3" s="110"/>
     </row>
     <row r="4" spans="1:28" ht="19.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
@@ -2654,48 +2654,48 @@
       <c r="A5" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="73"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="170"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="101"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="101"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="101"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="101"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="58">
+      <c r="B5" s="61"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="50"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="41"/>
+      <c r="S5" s="67"/>
+      <c r="T5" s="41"/>
+      <c r="U5" s="72"/>
+      <c r="V5" s="41">
         <f>MIN(9, SUM(B5, D5,F5,H5,J5, L5, N5, P5, R5, T5))</f>
         <v>0</v>
       </c>
-      <c r="W5" s="105">
+      <c r="W5" s="90">
         <f>MAX(0, SUM(B5,D5, F5,H5,J5, L5, N5, P5, R5, T5) - 9)</f>
         <v>0</v>
       </c>
-      <c r="X5" s="88">
+      <c r="X5" s="117">
         <f>SUM(B5, D5,F5,H5,J5, L5, N5, P5, R5, T5)</f>
         <v>0</v>
       </c>
-      <c r="Y5" s="152">
+      <c r="Y5" s="114">
         <f>C5</f>
         <v>0</v>
       </c>
-      <c r="Z5" s="78">
+      <c r="Z5" s="116">
         <f>SUM(E5+G5+I5+K5+M5+O5+Q5+S5+U5)</f>
         <v>0</v>
       </c>
-      <c r="AA5" s="78"/>
-      <c r="AB5" s="52">
+      <c r="AA5" s="116"/>
+      <c r="AB5" s="104">
         <f>SUM(Y5+Z5+AA5)</f>
         <v>0</v>
       </c>
@@ -2704,80 +2704,80 @@
       <c r="A6" s="38">
         <v>46244</v>
       </c>
-      <c r="B6" s="74"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="171"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="59"/>
-      <c r="K6" s="102"/>
-      <c r="L6" s="59"/>
-      <c r="M6" s="100"/>
-      <c r="N6" s="59"/>
-      <c r="O6" s="102"/>
-      <c r="P6" s="59"/>
-      <c r="Q6" s="102"/>
-      <c r="R6" s="59"/>
-      <c r="S6" s="102"/>
-      <c r="T6" s="59"/>
-      <c r="U6" s="104"/>
-      <c r="V6" s="59"/>
-      <c r="W6" s="79"/>
-      <c r="X6" s="89"/>
-      <c r="Y6" s="89"/>
-      <c r="Z6" s="79"/>
-      <c r="AA6" s="79"/>
-      <c r="AB6" s="53"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="68"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="68"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="68"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="46"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="68"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="68"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="68"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="42"/>
+      <c r="W6" s="91"/>
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="91"/>
+      <c r="AA6" s="91"/>
+      <c r="AB6" s="105"/>
     </row>
     <row r="7" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="73"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="73"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="170"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="58"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="58"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="58"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="58"/>
-      <c r="Q7" s="101"/>
-      <c r="R7" s="58"/>
-      <c r="S7" s="101"/>
-      <c r="T7" s="58"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="58">
+      <c r="B7" s="61"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="67"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="41"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="41"/>
+      <c r="M7" s="50"/>
+      <c r="N7" s="41"/>
+      <c r="O7" s="67"/>
+      <c r="P7" s="41"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="41"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="41"/>
+      <c r="U7" s="72"/>
+      <c r="V7" s="41">
         <f>MIN(9, SUM(B7, D7,F7,H7,J7, L7, N7, P7, R7, T7))</f>
         <v>0</v>
       </c>
-      <c r="W7" s="105">
+      <c r="W7" s="90">
         <f>MAX(0, SUM(B7,D7, F7,H7,J7, L7, N7, P7, R7, T7) - 9)</f>
         <v>0</v>
       </c>
-      <c r="X7" s="88">
+      <c r="X7" s="117">
         <f>SUM(B7, D7,F7,H7,J7, L7, N7, P7, R7, T7)</f>
         <v>0</v>
       </c>
-      <c r="Y7" s="152">
+      <c r="Y7" s="114">
         <f t="shared" ref="Y7:Y14" si="0">C7</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="78">
+      <c r="Z7" s="116">
         <f t="shared" ref="Z7:Z14" si="1">SUM(E7+G7+I7+K7+M7+O7+Q7+S7+U7)</f>
         <v>0</v>
       </c>
-      <c r="AA7" s="78"/>
-      <c r="AB7" s="52">
+      <c r="AA7" s="116"/>
+      <c r="AB7" s="104">
         <f t="shared" ref="AB7" si="2">SUM(Y7+Z7+AA7)</f>
         <v>0</v>
       </c>
@@ -2787,80 +2787,80 @@
         <f>A6+1</f>
         <v>46245</v>
       </c>
-      <c r="B8" s="74"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="74"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="171"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="59"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="59"/>
-      <c r="K8" s="102"/>
-      <c r="L8" s="59"/>
-      <c r="M8" s="100"/>
-      <c r="N8" s="59"/>
-      <c r="O8" s="102"/>
-      <c r="P8" s="59"/>
-      <c r="Q8" s="102"/>
-      <c r="R8" s="59"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="59"/>
-      <c r="U8" s="104"/>
-      <c r="V8" s="59"/>
-      <c r="W8" s="79"/>
-      <c r="X8" s="89"/>
-      <c r="Y8" s="89"/>
-      <c r="Z8" s="79"/>
-      <c r="AA8" s="79"/>
-      <c r="AB8" s="53"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="68"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="68"/>
+      <c r="J8" s="42"/>
+      <c r="K8" s="68"/>
+      <c r="L8" s="42"/>
+      <c r="M8" s="46"/>
+      <c r="N8" s="42"/>
+      <c r="O8" s="68"/>
+      <c r="P8" s="42"/>
+      <c r="Q8" s="68"/>
+      <c r="R8" s="42"/>
+      <c r="S8" s="68"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="47"/>
+      <c r="V8" s="42"/>
+      <c r="W8" s="91"/>
+      <c r="X8" s="115"/>
+      <c r="Y8" s="115"/>
+      <c r="Z8" s="91"/>
+      <c r="AA8" s="91"/>
+      <c r="AB8" s="105"/>
     </row>
     <row r="9" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="73"/>
-      <c r="C9" s="103"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="170"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="58"/>
-      <c r="K9" s="101"/>
-      <c r="L9" s="58"/>
-      <c r="M9" s="99"/>
-      <c r="N9" s="58"/>
-      <c r="O9" s="101"/>
-      <c r="P9" s="58"/>
-      <c r="Q9" s="101"/>
-      <c r="R9" s="58"/>
-      <c r="S9" s="101"/>
-      <c r="T9" s="58"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="58">
+      <c r="B9" s="61"/>
+      <c r="C9" s="72"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="41"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="50"/>
+      <c r="N9" s="41"/>
+      <c r="O9" s="67"/>
+      <c r="P9" s="41"/>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="41"/>
+      <c r="U9" s="72"/>
+      <c r="V9" s="41">
         <f>MIN(9, SUM(B9, D9,F9,H9,J9, L9, N9, P9, R9, T9))</f>
         <v>0</v>
       </c>
-      <c r="W9" s="105">
+      <c r="W9" s="90">
         <f>MAX(0, SUM(B9,D9, F9,H9,J9, L9, N9, P9, R9, T9) - 9)</f>
         <v>0</v>
       </c>
-      <c r="X9" s="88">
+      <c r="X9" s="117">
         <f>SUM(B9, D9,F9,H9,J9, L9, N9, P9, R9, T9)</f>
         <v>0</v>
       </c>
-      <c r="Y9" s="152">
+      <c r="Y9" s="114">
         <f t="shared" ref="Y9:Y14" si="3">C9</f>
         <v>0</v>
       </c>
-      <c r="Z9" s="78">
+      <c r="Z9" s="116">
         <f t="shared" ref="Z9:Z14" si="4">SUM(E9+G9+I9+K9+M9+O9+Q9+S9+U9)</f>
         <v>0</v>
       </c>
-      <c r="AA9" s="78"/>
-      <c r="AB9" s="52">
+      <c r="AA9" s="116"/>
+      <c r="AB9" s="104">
         <f t="shared" ref="AB9" si="5">SUM(Y9+Z9+AA9)</f>
         <v>0</v>
       </c>
@@ -2870,80 +2870,80 @@
         <f>A8+1</f>
         <v>46246</v>
       </c>
-      <c r="B10" s="74"/>
-      <c r="C10" s="104"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="100"/>
-      <c r="F10" s="171"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="59"/>
-      <c r="I10" s="102"/>
-      <c r="J10" s="59"/>
-      <c r="K10" s="102"/>
-      <c r="L10" s="59"/>
-      <c r="M10" s="100"/>
-      <c r="N10" s="59"/>
-      <c r="O10" s="102"/>
-      <c r="P10" s="59"/>
-      <c r="Q10" s="102"/>
-      <c r="R10" s="59"/>
-      <c r="S10" s="102"/>
-      <c r="T10" s="59"/>
-      <c r="U10" s="104"/>
-      <c r="V10" s="59"/>
-      <c r="W10" s="79"/>
-      <c r="X10" s="89"/>
-      <c r="Y10" s="89"/>
-      <c r="Z10" s="79"/>
-      <c r="AA10" s="79"/>
-      <c r="AB10" s="53"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="62"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="68"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="68"/>
+      <c r="J10" s="42"/>
+      <c r="K10" s="68"/>
+      <c r="L10" s="42"/>
+      <c r="M10" s="46"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="68"/>
+      <c r="P10" s="42"/>
+      <c r="Q10" s="68"/>
+      <c r="R10" s="42"/>
+      <c r="S10" s="68"/>
+      <c r="T10" s="42"/>
+      <c r="U10" s="47"/>
+      <c r="V10" s="42"/>
+      <c r="W10" s="91"/>
+      <c r="X10" s="115"/>
+      <c r="Y10" s="115"/>
+      <c r="Z10" s="91"/>
+      <c r="AA10" s="91"/>
+      <c r="AB10" s="105"/>
     </row>
     <row r="11" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="168"/>
-      <c r="C11" s="97"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="99"/>
-      <c r="F11" s="170"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="101"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="60"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="60"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="60"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="75"/>
-      <c r="V11" s="58">
+      <c r="B11" s="102"/>
+      <c r="C11" s="168"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="41"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="43"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="69"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="43"/>
+      <c r="U11" s="70"/>
+      <c r="V11" s="41">
         <f>MIN(9, SUM(B11, D11,F11,H11,J11, L11, N11, P11, R11, T11))</f>
         <v>0</v>
       </c>
-      <c r="W11" s="105">
+      <c r="W11" s="90">
         <f>MAX(0, SUM(B11,D11, F11,H11,J11, L11, N11, P11, R11, T11) - 9)</f>
         <v>0</v>
       </c>
-      <c r="X11" s="88">
+      <c r="X11" s="117">
         <f>SUM(B11, D11,F11,H11,J11, L11, N11, P11, R11, T11)</f>
         <v>0</v>
       </c>
-      <c r="Y11" s="152">
+      <c r="Y11" s="114">
         <f t="shared" ref="Y11:Y14" si="6">C11</f>
         <v>0</v>
       </c>
-      <c r="Z11" s="78">
+      <c r="Z11" s="116">
         <f t="shared" ref="Z11:Z14" si="7">SUM(E11+G11+I11+K11+M11+O11+Q11+S11+U11)</f>
         <v>0</v>
       </c>
-      <c r="AA11" s="82"/>
-      <c r="AB11" s="52">
+      <c r="AA11" s="106"/>
+      <c r="AB11" s="104">
         <f t="shared" ref="AB11" si="8">SUM(Y11+Z11+AA11)</f>
         <v>0</v>
       </c>
@@ -2953,80 +2953,80 @@
         <f>A10+1</f>
         <v>46247</v>
       </c>
-      <c r="B12" s="169"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="74"/>
-      <c r="E12" s="100"/>
-      <c r="F12" s="171"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="59"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="59"/>
-      <c r="M12" s="100"/>
-      <c r="N12" s="55"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="55"/>
-      <c r="Q12" s="81"/>
-      <c r="R12" s="55"/>
-      <c r="S12" s="81"/>
-      <c r="T12" s="55"/>
-      <c r="U12" s="76"/>
-      <c r="V12" s="59"/>
-      <c r="W12" s="79"/>
-      <c r="X12" s="89"/>
-      <c r="Y12" s="89"/>
-      <c r="Z12" s="79"/>
-      <c r="AA12" s="83"/>
-      <c r="AB12" s="53"/>
+      <c r="B12" s="103"/>
+      <c r="C12" s="169"/>
+      <c r="D12" s="62"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="68"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="68"/>
+      <c r="J12" s="42"/>
+      <c r="K12" s="68"/>
+      <c r="L12" s="42"/>
+      <c r="M12" s="46"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="83"/>
+      <c r="P12" s="44"/>
+      <c r="Q12" s="83"/>
+      <c r="R12" s="44"/>
+      <c r="S12" s="83"/>
+      <c r="T12" s="44"/>
+      <c r="U12" s="93"/>
+      <c r="V12" s="42"/>
+      <c r="W12" s="91"/>
+      <c r="X12" s="115"/>
+      <c r="Y12" s="115"/>
+      <c r="Z12" s="91"/>
+      <c r="AA12" s="107"/>
+      <c r="AB12" s="105"/>
     </row>
     <row r="13" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="166"/>
-      <c r="C13" s="75"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="170"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="101"/>
-      <c r="J13" s="58"/>
-      <c r="K13" s="101"/>
-      <c r="L13" s="58"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="54"/>
-      <c r="O13" s="60"/>
-      <c r="P13" s="54"/>
-      <c r="Q13" s="60"/>
-      <c r="R13" s="54"/>
-      <c r="S13" s="60"/>
-      <c r="T13" s="54"/>
-      <c r="U13" s="75"/>
-      <c r="V13" s="58">
+      <c r="B13" s="59"/>
+      <c r="C13" s="70"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="67"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="67"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="50"/>
+      <c r="N13" s="43"/>
+      <c r="O13" s="69"/>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="69"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="69"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="70"/>
+      <c r="V13" s="41">
         <f>MIN(9, SUM(B13, D13,F13,H13,J13, L13, N13, P13, R13, T13))</f>
         <v>0</v>
       </c>
-      <c r="W13" s="105">
+      <c r="W13" s="90">
         <f>MAX(0, SUM(B13,D13, F13,H13,J13, L13, N13, P13, R13, T13) - 9)</f>
         <v>0</v>
       </c>
-      <c r="X13" s="88">
+      <c r="X13" s="117">
         <f>SUM(B13, D13,F13,H13,J13, L13, N13, P13, R13, T13)</f>
         <v>0</v>
       </c>
-      <c r="Y13" s="152">
+      <c r="Y13" s="114">
         <f t="shared" ref="Y13:Y14" si="9">C13</f>
         <v>0</v>
       </c>
-      <c r="Z13" s="78">
+      <c r="Z13" s="116">
         <f t="shared" ref="Z13:Z14" si="10">SUM(E13+G13+I13+K13+M13+O13+Q13+S13+U13)</f>
         <v>0</v>
       </c>
-      <c r="AA13" s="82"/>
-      <c r="AB13" s="52">
+      <c r="AA13" s="106"/>
+      <c r="AB13" s="104">
         <f t="shared" ref="AB13" si="11">SUM(Y13+Z13+AA13)</f>
         <v>0</v>
       </c>
@@ -3036,163 +3036,163 @@
         <f>A12+1</f>
         <v>46248</v>
       </c>
-      <c r="B14" s="182"/>
-      <c r="C14" s="76"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="171"/>
-      <c r="G14" s="102"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="59"/>
-      <c r="K14" s="102"/>
-      <c r="L14" s="59"/>
-      <c r="M14" s="100"/>
-      <c r="N14" s="55"/>
-      <c r="O14" s="81"/>
-      <c r="P14" s="55"/>
-      <c r="Q14" s="81"/>
-      <c r="R14" s="55"/>
-      <c r="S14" s="81"/>
-      <c r="T14" s="55"/>
-      <c r="U14" s="76"/>
-      <c r="V14" s="59"/>
-      <c r="W14" s="79"/>
-      <c r="X14" s="89"/>
-      <c r="Y14" s="89"/>
-      <c r="Z14" s="79"/>
-      <c r="AA14" s="83"/>
-      <c r="AB14" s="53"/>
+      <c r="B14" s="60"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="68"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="68"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="68"/>
+      <c r="L14" s="42"/>
+      <c r="M14" s="46"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="83"/>
+      <c r="P14" s="44"/>
+      <c r="Q14" s="83"/>
+      <c r="R14" s="44"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="44"/>
+      <c r="U14" s="93"/>
+      <c r="V14" s="42"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="115"/>
+      <c r="Y14" s="115"/>
+      <c r="Z14" s="91"/>
+      <c r="AA14" s="107"/>
+      <c r="AB14" s="105"/>
     </row>
     <row r="15" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="166"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="166"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="60"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="60"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="60"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="60"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="60"/>
-      <c r="P15" s="54"/>
-      <c r="Q15" s="60"/>
-      <c r="R15" s="54"/>
-      <c r="S15" s="60"/>
-      <c r="T15" s="54"/>
-      <c r="U15" s="75"/>
-      <c r="V15" s="84"/>
-      <c r="W15" s="159"/>
-      <c r="X15" s="86"/>
-      <c r="Y15" s="157"/>
-      <c r="Z15" s="82"/>
-      <c r="AA15" s="82"/>
-      <c r="AB15" s="86"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="69"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="69"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="69"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="70"/>
+      <c r="V15" s="164"/>
+      <c r="W15" s="94"/>
+      <c r="X15" s="124"/>
+      <c r="Y15" s="122"/>
+      <c r="Z15" s="106"/>
+      <c r="AA15" s="106"/>
+      <c r="AB15" s="124"/>
     </row>
     <row r="16" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="38">
         <f>A14+1</f>
         <v>46249</v>
       </c>
-      <c r="B16" s="182"/>
-      <c r="C16" s="76"/>
-      <c r="D16" s="182"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="81"/>
-      <c r="H16" s="55"/>
-      <c r="I16" s="178"/>
-      <c r="J16" s="55"/>
-      <c r="K16" s="81"/>
-      <c r="L16" s="55"/>
-      <c r="M16" s="81"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="81"/>
-      <c r="P16" s="55"/>
-      <c r="Q16" s="81"/>
-      <c r="R16" s="55"/>
-      <c r="S16" s="81"/>
-      <c r="T16" s="55"/>
-      <c r="U16" s="76"/>
-      <c r="V16" s="92"/>
-      <c r="W16" s="179"/>
-      <c r="X16" s="93"/>
-      <c r="Y16" s="158"/>
-      <c r="Z16" s="83"/>
-      <c r="AA16" s="83"/>
-      <c r="AB16" s="93"/>
+      <c r="B16" s="60"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="60"/>
+      <c r="E16" s="83"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="83"/>
+      <c r="L16" s="44"/>
+      <c r="M16" s="83"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="83"/>
+      <c r="P16" s="44"/>
+      <c r="Q16" s="83"/>
+      <c r="R16" s="44"/>
+      <c r="S16" s="83"/>
+      <c r="T16" s="44"/>
+      <c r="U16" s="93"/>
+      <c r="V16" s="165"/>
+      <c r="W16" s="95"/>
+      <c r="X16" s="125"/>
+      <c r="Y16" s="133"/>
+      <c r="Z16" s="107"/>
+      <c r="AA16" s="107"/>
+      <c r="AB16" s="125"/>
     </row>
     <row r="17" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="166"/>
-      <c r="C17" s="75"/>
-      <c r="D17" s="166"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="129"/>
-      <c r="G17" s="60"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="183"/>
-      <c r="J17" s="54"/>
-      <c r="K17" s="60"/>
-      <c r="L17" s="54"/>
-      <c r="M17" s="60"/>
-      <c r="N17" s="54"/>
-      <c r="O17" s="60"/>
-      <c r="P17" s="54"/>
-      <c r="Q17" s="60"/>
-      <c r="R17" s="54"/>
-      <c r="S17" s="60"/>
-      <c r="T17" s="54"/>
-      <c r="U17" s="75"/>
-      <c r="V17" s="84"/>
-      <c r="W17" s="159"/>
-      <c r="X17" s="86"/>
-      <c r="Y17" s="157"/>
-      <c r="Z17" s="82"/>
-      <c r="AA17" s="82"/>
-      <c r="AB17" s="86"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="70"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="185"/>
+      <c r="F17" s="160"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="63"/>
+      <c r="J17" s="43"/>
+      <c r="K17" s="69"/>
+      <c r="L17" s="43"/>
+      <c r="M17" s="69"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="43"/>
+      <c r="Q17" s="69"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="43"/>
+      <c r="U17" s="70"/>
+      <c r="V17" s="164"/>
+      <c r="W17" s="94"/>
+      <c r="X17" s="124"/>
+      <c r="Y17" s="122"/>
+      <c r="Z17" s="106"/>
+      <c r="AA17" s="106"/>
+      <c r="AB17" s="124"/>
     </row>
     <row r="18" spans="1:28" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A18" s="38">
         <f>A16+1</f>
         <v>46250</v>
       </c>
-      <c r="B18" s="167"/>
-      <c r="C18" s="131"/>
-      <c r="D18" s="167"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="130"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="162"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="80"/>
-      <c r="M18" s="111"/>
-      <c r="N18" s="162"/>
-      <c r="O18" s="61"/>
-      <c r="P18" s="162"/>
-      <c r="Q18" s="111"/>
-      <c r="R18" s="80"/>
-      <c r="S18" s="111"/>
-      <c r="T18" s="80"/>
-      <c r="U18" s="131"/>
-      <c r="V18" s="85"/>
-      <c r="W18" s="160"/>
-      <c r="X18" s="87"/>
-      <c r="Y18" s="165"/>
-      <c r="Z18" s="94"/>
-      <c r="AA18" s="94"/>
-      <c r="AB18" s="87"/>
+      <c r="B18" s="96"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="186"/>
+      <c r="F18" s="161"/>
+      <c r="G18" s="130"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="64"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="64"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="64"/>
+      <c r="N18" s="84"/>
+      <c r="O18" s="130"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="64"/>
+      <c r="R18" s="98"/>
+      <c r="S18" s="64"/>
+      <c r="T18" s="98"/>
+      <c r="U18" s="71"/>
+      <c r="V18" s="188"/>
+      <c r="W18" s="134"/>
+      <c r="X18" s="137"/>
+      <c r="Y18" s="123"/>
+      <c r="Z18" s="126"/>
+      <c r="AA18" s="126"/>
+      <c r="AB18" s="137"/>
     </row>
     <row r="19" spans="1:28" ht="12.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
@@ -3308,36 +3308,36 @@
       </c>
     </row>
     <row r="20" spans="1:28" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="185" t="s">
+      <c r="A20" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="68"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="67"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="68"/>
-      <c r="O20" s="68"/>
-      <c r="P20" s="68"/>
-      <c r="Q20" s="68"/>
-      <c r="R20" s="68"/>
-      <c r="S20" s="68"/>
-      <c r="T20" s="68"/>
-      <c r="U20" s="68"/>
-      <c r="V20" s="68"/>
-      <c r="W20" s="68"/>
-      <c r="X20" s="68"/>
-      <c r="Y20" s="68"/>
-      <c r="Z20" s="68"/>
-      <c r="AA20" s="68"/>
-      <c r="AB20" s="69"/>
+      <c r="B20" s="66"/>
+      <c r="C20" s="66"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="66"/>
+      <c r="F20" s="66"/>
+      <c r="G20" s="66"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="66"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="66"/>
+      <c r="M20" s="66"/>
+      <c r="N20" s="66"/>
+      <c r="O20" s="66"/>
+      <c r="P20" s="66"/>
+      <c r="Q20" s="66"/>
+      <c r="R20" s="66"/>
+      <c r="S20" s="66"/>
+      <c r="T20" s="66"/>
+      <c r="U20" s="66"/>
+      <c r="V20" s="66"/>
+      <c r="W20" s="66"/>
+      <c r="X20" s="66"/>
+      <c r="Y20" s="66"/>
+      <c r="Z20" s="66"/>
+      <c r="AA20" s="66"/>
+      <c r="AB20" s="82"/>
     </row>
     <row r="21" spans="1:28" ht="22.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="17" t="s">
@@ -3363,395 +3363,395 @@
       <c r="S21" s="19"/>
       <c r="T21" s="19"/>
       <c r="U21" s="20"/>
-      <c r="V21" s="154" t="s">
+      <c r="V21" s="131" t="s">
         <v>27</v>
       </c>
-      <c r="W21" s="155"/>
-      <c r="X21" s="156"/>
-      <c r="Y21" s="145" t="s">
+      <c r="W21" s="132"/>
+      <c r="X21" s="119"/>
+      <c r="Y21" s="148" t="s">
         <v>28</v>
       </c>
-      <c r="Z21" s="146"/>
-      <c r="AA21" s="163"/>
-      <c r="AB21" s="156"/>
+      <c r="Z21" s="149"/>
+      <c r="AA21" s="118"/>
+      <c r="AB21" s="119"/>
     </row>
     <row r="22" spans="1:28" ht="21.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A22" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="153"/>
-      <c r="C22" s="115"/>
-      <c r="D22" s="153"/>
-      <c r="E22" s="115"/>
-      <c r="F22" s="153"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="153"/>
-      <c r="I22" s="115"/>
-      <c r="J22" s="114"/>
-      <c r="K22" s="115"/>
-      <c r="L22" s="114"/>
-      <c r="M22" s="115"/>
-      <c r="N22" s="114"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="115"/>
-      <c r="R22" s="114"/>
-      <c r="S22" s="115"/>
-      <c r="T22" s="161"/>
-      <c r="U22" s="72"/>
-      <c r="V22" s="147"/>
-      <c r="W22" s="71"/>
-      <c r="X22" s="71"/>
-      <c r="Y22" s="136" t="s">
+      <c r="B22" s="48"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="48"/>
+      <c r="E22" s="49"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="48"/>
+      <c r="I22" s="49"/>
+      <c r="J22" s="51"/>
+      <c r="K22" s="49"/>
+      <c r="L22" s="51"/>
+      <c r="M22" s="49"/>
+      <c r="N22" s="51"/>
+      <c r="O22" s="49"/>
+      <c r="P22" s="51"/>
+      <c r="Q22" s="49"/>
+      <c r="R22" s="51"/>
+      <c r="S22" s="49"/>
+      <c r="T22" s="135"/>
+      <c r="U22" s="78"/>
+      <c r="V22" s="150"/>
+      <c r="W22" s="77"/>
+      <c r="X22" s="77"/>
+      <c r="Y22" s="139" t="s">
         <v>30</v>
       </c>
-      <c r="Z22" s="137"/>
-      <c r="AA22" s="144"/>
-      <c r="AB22" s="104"/>
+      <c r="Z22" s="140"/>
+      <c r="AA22" s="147"/>
+      <c r="AB22" s="47"/>
     </row>
     <row r="23" spans="1:28" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="46"/>
-      <c r="B23" s="47"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="39">
+      <c r="A23" s="179"/>
+      <c r="B23" s="180"/>
+      <c r="C23" s="180"/>
+      <c r="D23" s="172">
         <f>A18+1</f>
         <v>46251</v>
       </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="41"/>
-      <c r="G23" s="135"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="63"/>
-      <c r="J23" s="63"/>
-      <c r="K23" s="63"/>
-      <c r="L23" s="63"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="180" t="s">
+      <c r="E23" s="173"/>
+      <c r="F23" s="174"/>
+      <c r="G23" s="138"/>
+      <c r="H23" s="86"/>
+      <c r="I23" s="86"/>
+      <c r="J23" s="86"/>
+      <c r="K23" s="86"/>
+      <c r="L23" s="86"/>
+      <c r="M23" s="86"/>
+      <c r="N23" s="87"/>
+      <c r="O23" s="97" t="s">
         <v>31</v>
       </c>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="63"/>
-      <c r="S23" s="63"/>
-      <c r="T23" s="63"/>
-      <c r="U23" s="63"/>
-      <c r="V23" s="63"/>
-      <c r="W23" s="63"/>
-      <c r="X23" s="63"/>
-      <c r="Y23" s="136" t="s">
+      <c r="P23" s="86"/>
+      <c r="Q23" s="86"/>
+      <c r="R23" s="86"/>
+      <c r="S23" s="86"/>
+      <c r="T23" s="86"/>
+      <c r="U23" s="86"/>
+      <c r="V23" s="86"/>
+      <c r="W23" s="86"/>
+      <c r="X23" s="86"/>
+      <c r="Y23" s="139" t="s">
         <v>32</v>
       </c>
-      <c r="Z23" s="118"/>
-      <c r="AA23" s="142">
+      <c r="Z23" s="121"/>
+      <c r="AA23" s="145">
         <f>AB19</f>
         <v>0</v>
       </c>
-      <c r="AB23" s="124"/>
+      <c r="AB23" s="75"/>
     </row>
     <row r="24" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="48"/>
-      <c r="B24" s="49"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="42"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="66"/>
-      <c r="I24" s="67"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="69"/>
-      <c r="O24" s="151" t="s">
+      <c r="A24" s="181"/>
+      <c r="B24" s="182"/>
+      <c r="C24" s="182"/>
+      <c r="D24" s="175"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="176"/>
+      <c r="G24" s="88"/>
+      <c r="H24" s="80"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="66"/>
+      <c r="K24" s="66"/>
+      <c r="L24" s="66"/>
+      <c r="M24" s="66"/>
+      <c r="N24" s="82"/>
+      <c r="O24" s="154" t="s">
         <v>33</v>
       </c>
-      <c r="P24" s="68"/>
-      <c r="Q24" s="77"/>
-      <c r="R24" s="68"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="128"/>
+      <c r="R24" s="66"/>
       <c r="S24" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="T24" s="77"/>
-      <c r="U24" s="68"/>
-      <c r="V24" s="68"/>
+      <c r="T24" s="128"/>
+      <c r="U24" s="66"/>
+      <c r="V24" s="66"/>
       <c r="W24" s="23" t="s">
         <v>35</v>
       </c>
       <c r="X24" s="27"/>
-      <c r="Y24" s="148"/>
-      <c r="Z24" s="149"/>
-      <c r="AA24" s="143"/>
-      <c r="AB24" s="104"/>
+      <c r="Y24" s="151"/>
+      <c r="Z24" s="152"/>
+      <c r="AA24" s="146"/>
+      <c r="AB24" s="47"/>
     </row>
     <row r="25" spans="1:28" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="50"/>
-      <c r="B25" s="51"/>
-      <c r="C25" s="51"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="67"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="69"/>
-      <c r="O25" s="184" t="s">
+      <c r="A25" s="183"/>
+      <c r="B25" s="184"/>
+      <c r="C25" s="184"/>
+      <c r="D25" s="177"/>
+      <c r="E25" s="177"/>
+      <c r="F25" s="178"/>
+      <c r="G25" s="88"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="66"/>
+      <c r="K25" s="66"/>
+      <c r="L25" s="66"/>
+      <c r="M25" s="66"/>
+      <c r="N25" s="82"/>
+      <c r="O25" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="P25" s="68"/>
-      <c r="Q25" s="186"/>
-      <c r="R25" s="100"/>
-      <c r="S25" s="100"/>
-      <c r="T25" s="100"/>
-      <c r="U25" s="100"/>
-      <c r="V25" s="100"/>
-      <c r="W25" s="100"/>
-      <c r="X25" s="104"/>
-      <c r="Y25" s="136" t="s">
+      <c r="P25" s="66"/>
+      <c r="Q25" s="45"/>
+      <c r="R25" s="46"/>
+      <c r="S25" s="46"/>
+      <c r="T25" s="46"/>
+      <c r="U25" s="46"/>
+      <c r="V25" s="46"/>
+      <c r="W25" s="46"/>
+      <c r="X25" s="47"/>
+      <c r="Y25" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="Z25" s="137"/>
-      <c r="AA25" s="142">
+      <c r="Z25" s="140"/>
+      <c r="AA25" s="145">
         <f>Y19+Z19</f>
         <v>0</v>
       </c>
-      <c r="AB25" s="140"/>
+      <c r="AB25" s="143"/>
     </row>
     <row r="26" spans="1:28" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="116" t="s">
+      <c r="A26" s="127" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="117"/>
-      <c r="C26" s="118"/>
-      <c r="D26" s="123" t="s">
+      <c r="B26" s="74"/>
+      <c r="C26" s="121"/>
+      <c r="D26" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="E26" s="117"/>
-      <c r="F26" s="124"/>
-      <c r="G26" s="116" t="s">
+      <c r="E26" s="74"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="127" t="s">
         <v>39</v>
       </c>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="117"/>
-      <c r="K26" s="118"/>
-      <c r="L26" s="123" t="s">
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
+      <c r="J26" s="74"/>
+      <c r="K26" s="121"/>
+      <c r="L26" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="M26" s="117"/>
-      <c r="N26" s="124"/>
-      <c r="O26" s="184" t="s">
+      <c r="M26" s="74"/>
+      <c r="N26" s="75"/>
+      <c r="O26" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="P26" s="68"/>
-      <c r="Q26" s="138"/>
-      <c r="R26" s="139"/>
-      <c r="S26" s="139"/>
-      <c r="T26" s="139"/>
-      <c r="U26" s="139"/>
-      <c r="V26" s="139"/>
-      <c r="W26" s="139"/>
-      <c r="X26" s="140"/>
-      <c r="Y26" s="164" t="s">
+      <c r="P26" s="66"/>
+      <c r="Q26" s="141"/>
+      <c r="R26" s="142"/>
+      <c r="S26" s="142"/>
+      <c r="T26" s="142"/>
+      <c r="U26" s="142"/>
+      <c r="V26" s="142"/>
+      <c r="W26" s="142"/>
+      <c r="X26" s="143"/>
+      <c r="Y26" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="Z26" s="118"/>
-      <c r="AA26" s="141">
+      <c r="Z26" s="121"/>
+      <c r="AA26" s="144">
         <f>AA23-AA25</f>
         <v>0</v>
       </c>
-      <c r="AB26" s="124"/>
+      <c r="AB26" s="75"/>
     </row>
     <row r="27" spans="1:28" ht="3.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="70"/>
-      <c r="B27" s="71"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="125"/>
-      <c r="E27" s="71"/>
-      <c r="F27" s="72"/>
-      <c r="G27" s="70"/>
-      <c r="H27" s="71"/>
-      <c r="I27" s="71"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="115"/>
-      <c r="L27" s="125"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="72"/>
-      <c r="O27" s="150"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="71"/>
-      <c r="S27" s="71"/>
-      <c r="T27" s="71"/>
-      <c r="U27" s="71"/>
-      <c r="V27" s="71"/>
-      <c r="W27" s="71"/>
-      <c r="X27" s="72"/>
-      <c r="Y27" s="70"/>
-      <c r="Z27" s="115"/>
-      <c r="AA27" s="125"/>
-      <c r="AB27" s="72"/>
+      <c r="A27" s="89"/>
+      <c r="B27" s="77"/>
+      <c r="C27" s="49"/>
+      <c r="D27" s="76"/>
+      <c r="E27" s="77"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="77"/>
+      <c r="I27" s="77"/>
+      <c r="J27" s="77"/>
+      <c r="K27" s="49"/>
+      <c r="L27" s="76"/>
+      <c r="M27" s="77"/>
+      <c r="N27" s="78"/>
+      <c r="O27" s="153"/>
+      <c r="P27" s="77"/>
+      <c r="Q27" s="77"/>
+      <c r="R27" s="77"/>
+      <c r="S27" s="77"/>
+      <c r="T27" s="77"/>
+      <c r="U27" s="77"/>
+      <c r="V27" s="77"/>
+      <c r="W27" s="77"/>
+      <c r="X27" s="78"/>
+      <c r="Y27" s="89"/>
+      <c r="Z27" s="49"/>
+      <c r="AA27" s="76"/>
+      <c r="AB27" s="78"/>
     </row>
     <row r="28" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="177"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="64"/>
-      <c r="G28" s="62" t="s">
+      <c r="A28" s="85"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
+      <c r="D28" s="86"/>
+      <c r="E28" s="86"/>
+      <c r="F28" s="87"/>
+      <c r="G28" s="187" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="63"/>
-      <c r="I28" s="63"/>
-      <c r="J28" s="63"/>
-      <c r="K28" s="63"/>
-      <c r="L28" s="63"/>
-      <c r="M28" s="63"/>
-      <c r="N28" s="63"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
-      <c r="R28" s="63"/>
-      <c r="S28" s="63"/>
-      <c r="T28" s="63"/>
-      <c r="U28" s="63"/>
-      <c r="V28" s="63"/>
-      <c r="W28" s="64"/>
-      <c r="X28" s="134" t="s">
+      <c r="H28" s="86"/>
+      <c r="I28" s="86"/>
+      <c r="J28" s="86"/>
+      <c r="K28" s="86"/>
+      <c r="L28" s="86"/>
+      <c r="M28" s="86"/>
+      <c r="N28" s="86"/>
+      <c r="O28" s="86"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="86"/>
+      <c r="S28" s="86"/>
+      <c r="T28" s="86"/>
+      <c r="U28" s="86"/>
+      <c r="V28" s="86"/>
+      <c r="W28" s="87"/>
+      <c r="X28" s="136" t="s">
         <v>43</v>
       </c>
-      <c r="Y28" s="68"/>
-      <c r="Z28" s="68"/>
-      <c r="AA28" s="68"/>
-      <c r="AB28" s="69"/>
+      <c r="Y28" s="66"/>
+      <c r="Z28" s="66"/>
+      <c r="AA28" s="66"/>
+      <c r="AB28" s="82"/>
     </row>
     <row r="29" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="65"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="67"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="68"/>
-      <c r="M29" s="68"/>
-      <c r="N29" s="68"/>
-      <c r="O29" s="68"/>
-      <c r="P29" s="68"/>
-      <c r="Q29" s="68"/>
-      <c r="R29" s="68"/>
-      <c r="S29" s="68"/>
-      <c r="T29" s="68"/>
-      <c r="U29" s="68"/>
-      <c r="V29" s="68"/>
-      <c r="W29" s="69"/>
-      <c r="X29" s="65"/>
-      <c r="Y29" s="68"/>
-      <c r="Z29" s="68"/>
-      <c r="AA29" s="68"/>
-      <c r="AB29" s="69"/>
+      <c r="A29" s="88"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="80"/>
+      <c r="E29" s="66"/>
+      <c r="F29" s="82"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="66"/>
+      <c r="L29" s="66"/>
+      <c r="M29" s="66"/>
+      <c r="N29" s="66"/>
+      <c r="O29" s="66"/>
+      <c r="P29" s="66"/>
+      <c r="Q29" s="66"/>
+      <c r="R29" s="66"/>
+      <c r="S29" s="66"/>
+      <c r="T29" s="66"/>
+      <c r="U29" s="66"/>
+      <c r="V29" s="66"/>
+      <c r="W29" s="82"/>
+      <c r="X29" s="88"/>
+      <c r="Y29" s="66"/>
+      <c r="Z29" s="66"/>
+      <c r="AA29" s="66"/>
+      <c r="AB29" s="82"/>
     </row>
     <row r="30" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="65"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69"/>
-      <c r="G30" s="65"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
-      <c r="M30" s="68"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="68"/>
-      <c r="P30" s="68"/>
-      <c r="Q30" s="68"/>
-      <c r="R30" s="68"/>
-      <c r="S30" s="68"/>
-      <c r="T30" s="68"/>
-      <c r="U30" s="68"/>
-      <c r="V30" s="68"/>
-      <c r="W30" s="69"/>
-      <c r="X30" s="65"/>
-      <c r="Y30" s="68"/>
-      <c r="Z30" s="68"/>
-      <c r="AA30" s="68"/>
-      <c r="AB30" s="69"/>
+      <c r="A30" s="88"/>
+      <c r="B30" s="66"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="80"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="82"/>
+      <c r="G30" s="88"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="66"/>
+      <c r="K30" s="66"/>
+      <c r="L30" s="66"/>
+      <c r="M30" s="66"/>
+      <c r="N30" s="66"/>
+      <c r="O30" s="66"/>
+      <c r="P30" s="66"/>
+      <c r="Q30" s="66"/>
+      <c r="R30" s="66"/>
+      <c r="S30" s="66"/>
+      <c r="T30" s="66"/>
+      <c r="U30" s="66"/>
+      <c r="V30" s="66"/>
+      <c r="W30" s="82"/>
+      <c r="X30" s="88"/>
+      <c r="Y30" s="66"/>
+      <c r="Z30" s="66"/>
+      <c r="AA30" s="66"/>
+      <c r="AB30" s="82"/>
     </row>
     <row r="31" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="65"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="66"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69"/>
-      <c r="G31" s="65"/>
-      <c r="H31" s="66"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="68"/>
-      <c r="M31" s="68"/>
-      <c r="N31" s="68"/>
-      <c r="O31" s="68"/>
-      <c r="P31" s="68"/>
-      <c r="Q31" s="68"/>
-      <c r="R31" s="68"/>
-      <c r="S31" s="68"/>
-      <c r="T31" s="68"/>
-      <c r="U31" s="68"/>
-      <c r="V31" s="68"/>
-      <c r="W31" s="69"/>
-      <c r="X31" s="181" t="s">
+      <c r="A31" s="88"/>
+      <c r="B31" s="66"/>
+      <c r="C31" s="66"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="66"/>
+      <c r="F31" s="82"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="66"/>
+      <c r="K31" s="66"/>
+      <c r="L31" s="66"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="66"/>
+      <c r="O31" s="66"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="66"/>
+      <c r="R31" s="66"/>
+      <c r="S31" s="66"/>
+      <c r="T31" s="66"/>
+      <c r="U31" s="66"/>
+      <c r="V31" s="66"/>
+      <c r="W31" s="82"/>
+      <c r="X31" s="99" t="s">
         <v>44</v>
       </c>
-      <c r="Y31" s="68"/>
-      <c r="Z31" s="68"/>
-      <c r="AA31" s="68"/>
-      <c r="AB31" s="69"/>
+      <c r="Y31" s="66"/>
+      <c r="Z31" s="66"/>
+      <c r="AA31" s="66"/>
+      <c r="AB31" s="82"/>
     </row>
     <row r="32" spans="1:28" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="70"/>
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="72"/>
-      <c r="G32" s="70"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="71"/>
-      <c r="P32" s="71"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="71"/>
-      <c r="S32" s="71"/>
-      <c r="T32" s="71"/>
-      <c r="U32" s="71"/>
-      <c r="V32" s="71"/>
-      <c r="W32" s="72"/>
-      <c r="X32" s="70"/>
-      <c r="Y32" s="71"/>
-      <c r="Z32" s="71"/>
-      <c r="AA32" s="71"/>
-      <c r="AB32" s="72"/>
+      <c r="A32" s="89"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
+      <c r="E32" s="77"/>
+      <c r="F32" s="78"/>
+      <c r="G32" s="89"/>
+      <c r="H32" s="77"/>
+      <c r="I32" s="77"/>
+      <c r="J32" s="77"/>
+      <c r="K32" s="77"/>
+      <c r="L32" s="77"/>
+      <c r="M32" s="77"/>
+      <c r="N32" s="77"/>
+      <c r="O32" s="77"/>
+      <c r="P32" s="77"/>
+      <c r="Q32" s="77"/>
+      <c r="R32" s="77"/>
+      <c r="S32" s="77"/>
+      <c r="T32" s="77"/>
+      <c r="U32" s="77"/>
+      <c r="V32" s="77"/>
+      <c r="W32" s="78"/>
+      <c r="X32" s="89"/>
+      <c r="Y32" s="77"/>
+      <c r="Z32" s="77"/>
+      <c r="AA32" s="77"/>
+      <c r="AB32" s="78"/>
     </row>
     <row r="33" ht="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="34" ht="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -4723,6 +4723,241 @@
     <row r="1000" ht="12.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="259">
+    <mergeCell ref="D23:F25"/>
+    <mergeCell ref="A23:C25"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="J13:J14"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="L13:L14"/>
+    <mergeCell ref="G28:W32"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="J17:J18"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="L17:L18"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="V17:V18"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="X17:X18"/>
+    <mergeCell ref="X11:X12"/>
+    <mergeCell ref="O15:O16"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="V15:V16"/>
+    <mergeCell ref="X15:X16"/>
+    <mergeCell ref="Z17:Z18"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="I5:I6"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="I13:I14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="R3:S3"/>
+    <mergeCell ref="R2:S2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="X13:X14"/>
+    <mergeCell ref="S17:S18"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="R22:S22"/>
+    <mergeCell ref="A26:C27"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="P5:P6"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="P3:Q3"/>
+    <mergeCell ref="R5:R6"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L26:N27"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="K1:R1"/>
+    <mergeCell ref="U13:U14"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="U17:U18"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="X28:AB30"/>
+    <mergeCell ref="AB17:AB18"/>
+    <mergeCell ref="G23:N25"/>
+    <mergeCell ref="AB11:AB12"/>
+    <mergeCell ref="Q15:Q16"/>
+    <mergeCell ref="S15:S16"/>
+    <mergeCell ref="Y22:Z22"/>
+    <mergeCell ref="Q26:X26"/>
+    <mergeCell ref="AA26:AB27"/>
+    <mergeCell ref="AA23:AB24"/>
+    <mergeCell ref="Y25:Z25"/>
+    <mergeCell ref="AA25:AB25"/>
+    <mergeCell ref="AA22:AB22"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="P15:P16"/>
+    <mergeCell ref="Y21:Z21"/>
+    <mergeCell ref="V22:X22"/>
+    <mergeCell ref="Y23:Z24"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="L15:L16"/>
+    <mergeCell ref="O27:X27"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="Y13:Y14"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="T13:T14"/>
+    <mergeCell ref="O17:O18"/>
+    <mergeCell ref="Q17:Q18"/>
+    <mergeCell ref="V21:X21"/>
+    <mergeCell ref="Y15:Y16"/>
+    <mergeCell ref="W17:W18"/>
+    <mergeCell ref="T22:U22"/>
+    <mergeCell ref="P17:P18"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="AA21:AB21"/>
+    <mergeCell ref="Y26:Z27"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="Y17:Y18"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="Z15:Z16"/>
+    <mergeCell ref="AB15:AB16"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="AA17:AA18"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="G26:K27"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="Z7:Z8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="U11:U12"/>
+    <mergeCell ref="W5:W6"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="Y5:Y6"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="Y7:Y8"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="W11:W12"/>
+    <mergeCell ref="T11:T12"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="Z5:Z6"/>
+    <mergeCell ref="Y11:Y12"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="Z11:Z12"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="F5:F6"/>
+    <mergeCell ref="AB9:AB10"/>
+    <mergeCell ref="AA15:AA16"/>
+    <mergeCell ref="Y2:AB3"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="V2:X3"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="M13:M14"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="R17:R18"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="A28:F32"/>
+    <mergeCell ref="T15:T16"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="W13:W14"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="K15:K16"/>
+    <mergeCell ref="U15:U16"/>
+    <mergeCell ref="W15:W16"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="O23:X23"/>
+    <mergeCell ref="T17:T18"/>
+    <mergeCell ref="V11:V12"/>
+    <mergeCell ref="X31:AB32"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="N13:N14"/>
+    <mergeCell ref="P13:P14"/>
+    <mergeCell ref="K17:K18"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="I17:I18"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="G5:G6"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="M17:M18"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="C5:C6"/>
+    <mergeCell ref="E5:E6"/>
+    <mergeCell ref="D26:F27"/>
+    <mergeCell ref="A20:AB20"/>
+    <mergeCell ref="M15:M16"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="N17:N18"/>
+    <mergeCell ref="S13:S14"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="H9:H10"/>
     <mergeCell ref="R13:R14"/>
@@ -4747,241 +4982,6 @@
     <mergeCell ref="L22:M22"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="H3:I3"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="I17:I18"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="G5:G6"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="M17:M18"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="E5:E6"/>
-    <mergeCell ref="D26:F27"/>
-    <mergeCell ref="A20:AB20"/>
-    <mergeCell ref="M15:M16"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="N17:N18"/>
-    <mergeCell ref="S13:S14"/>
-    <mergeCell ref="A28:F32"/>
-    <mergeCell ref="T15:T16"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="W13:W14"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="K15:K16"/>
-    <mergeCell ref="U15:U16"/>
-    <mergeCell ref="W15:W16"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="O23:X23"/>
-    <mergeCell ref="T17:T18"/>
-    <mergeCell ref="V11:V12"/>
-    <mergeCell ref="X31:AB32"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="N13:N14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="K17:K18"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="F5:F6"/>
-    <mergeCell ref="AB9:AB10"/>
-    <mergeCell ref="AA15:AA16"/>
-    <mergeCell ref="Y2:AB3"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="V2:X3"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="M13:M14"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="R17:R18"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="W5:W6"/>
-    <mergeCell ref="Y9:Y10"/>
-    <mergeCell ref="Y5:Y6"/>
-    <mergeCell ref="AA9:AA10"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="W11:W12"/>
-    <mergeCell ref="T11:T12"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="Z5:Z6"/>
-    <mergeCell ref="Y11:Y12"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="Z11:Z12"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="AA21:AB21"/>
-    <mergeCell ref="Y26:Z27"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="Y17:Y18"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="Z15:Z16"/>
-    <mergeCell ref="AB15:AB16"/>
-    <mergeCell ref="I9:I10"/>
-    <mergeCell ref="AA17:AA18"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="G26:K27"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="Z7:Z8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="U11:U12"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="Y13:Y14"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="X9:X10"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="T13:T14"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="Q17:Q18"/>
-    <mergeCell ref="V21:X21"/>
-    <mergeCell ref="Y15:Y16"/>
-    <mergeCell ref="W17:W18"/>
-    <mergeCell ref="T22:U22"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="X28:AB30"/>
-    <mergeCell ref="AB17:AB18"/>
-    <mergeCell ref="G23:N25"/>
-    <mergeCell ref="AB11:AB12"/>
-    <mergeCell ref="Q15:Q16"/>
-    <mergeCell ref="S15:S16"/>
-    <mergeCell ref="Y22:Z22"/>
-    <mergeCell ref="Q26:X26"/>
-    <mergeCell ref="AA26:AB27"/>
-    <mergeCell ref="AA23:AB24"/>
-    <mergeCell ref="Y25:Z25"/>
-    <mergeCell ref="AA25:AB25"/>
-    <mergeCell ref="AA22:AB22"/>
-    <mergeCell ref="Z13:Z14"/>
-    <mergeCell ref="AB13:AB14"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Y21:Z21"/>
-    <mergeCell ref="V22:X22"/>
-    <mergeCell ref="Y23:Z24"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="L15:L16"/>
-    <mergeCell ref="O27:X27"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="R22:S22"/>
-    <mergeCell ref="A26:C27"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R5:R6"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L26:N27"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="K1:R1"/>
-    <mergeCell ref="U13:U14"/>
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="U17:U18"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="V15:V16"/>
-    <mergeCell ref="X15:X16"/>
-    <mergeCell ref="Z17:Z18"/>
-    <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="I5:I6"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="W9:W10"/>
-    <mergeCell ref="I13:I14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="R2:S2"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="V13:V14"/>
-    <mergeCell ref="X13:X14"/>
-    <mergeCell ref="S17:S18"/>
-    <mergeCell ref="D23:F25"/>
-    <mergeCell ref="A23:C25"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="E17:E18"/>
-    <mergeCell ref="J13:J14"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="L13:L14"/>
-    <mergeCell ref="G28:W32"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="Z9:Z10"/>
-    <mergeCell ref="J17:J18"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="L17:L18"/>
-    <mergeCell ref="Q13:Q14"/>
-    <mergeCell ref="AA13:AA14"/>
-    <mergeCell ref="V17:V18"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="X17:X18"/>
-    <mergeCell ref="X11:X12"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.55118110236220474" bottom="0.74803149606299213" header="0" footer="0"/>
